--- a/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
+++ b/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\信息收集整理\医生画像仓库\99_资料来源\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EE12E6-AC9E-4E4B-9921-BE575405BC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A85C5E-1A73-4254-B6E2-E62CCF338957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2803" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="819">
   <si>
     <t>序号</t>
   </si>
@@ -2494,7 +2494,61 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.gyfyyy.cn/cn/ylfw/czcx/</t>
+    <t>http://www.gzhtcm3.com/</t>
+  </si>
+  <si>
+    <t>http://www.gzhtcm3.com/wsjs/zzts.htm</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gyfyyy.cn/cn/ks/</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gy3y.cn/ks/team.html</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>广州医科大学附属第二医院</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gyey.com/cn/index.html</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gyey.com/cn/ks/team.html</t>
+  </si>
+  <si>
+    <t>广州医科大学附属脑科医院</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gzbrain.cn/</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gzbrain.cn/myzj/list.html</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gzbrain.cn/myzj/list.aspx</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>广州医科大学附属脑科医院(江村院区)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>广州市中医院</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gzszyy.com/patient/</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gzszyy.com/expert/</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4751,9 +4805,13 @@
       <c r="H28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I28" s="4"/>
+      <c r="I28" s="4" t="s">
+        <v>804</v>
+      </c>
       <c r="J28" s="2"/>
-      <c r="K28" s="4"/>
+      <c r="K28" s="6" t="s">
+        <v>805</v>
+      </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -4774,7 +4832,9 @@
       <c r="U28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V28" s="2"/>
+      <c r="V28" s="2" t="s">
+        <v>774</v>
+      </c>
       <c r="W28" s="2"/>
       <c r="X28" s="2" t="s">
         <v>36</v>
@@ -4797,7 +4857,7 @@
         <v>795</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>200</v>
+        <v>795</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>29</v>
@@ -5168,7 +5228,7 @@
         <v>232</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>56</v>
@@ -5200,7 +5260,9 @@
       <c r="U35" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V35" s="2"/>
+      <c r="V35" s="2" t="s">
+        <v>774</v>
+      </c>
       <c r="W35" s="2"/>
       <c r="X35" s="2" t="s">
         <v>36</v>
@@ -5237,8 +5299,8 @@
       <c r="J36" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="K36" s="4" t="s">
-        <v>241</v>
+      <c r="K36" s="6" t="s">
+        <v>807</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>99</v>
@@ -5270,7 +5332,9 @@
       <c r="U36" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V36" s="2"/>
+      <c r="V36" s="2" t="s">
+        <v>774</v>
+      </c>
       <c r="W36" s="2"/>
       <c r="X36" s="2" t="s">
         <v>36</v>
@@ -5290,7 +5354,7 @@
         <v>38</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>246</v>
+        <v>808</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>247</v>
@@ -5301,9 +5365,13 @@
       <c r="H37" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I37" s="4"/>
+      <c r="I37" s="6" t="s">
+        <v>809</v>
+      </c>
       <c r="J37" s="2"/>
-      <c r="K37" s="4"/>
+      <c r="K37" s="4" t="s">
+        <v>810</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -5324,7 +5392,9 @@
       <c r="U37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V37" s="2"/>
+      <c r="V37" s="2" t="s">
+        <v>774</v>
+      </c>
       <c r="W37" s="2"/>
       <c r="X37" s="2" t="s">
         <v>36</v>
@@ -5344,7 +5414,7 @@
         <v>152</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>250</v>
+        <v>811</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>250</v>
@@ -5355,9 +5425,13 @@
       <c r="H38" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I38" s="4"/>
+      <c r="I38" s="6" t="s">
+        <v>812</v>
+      </c>
       <c r="J38" s="2"/>
-      <c r="K38" s="4"/>
+      <c r="K38" s="6" t="s">
+        <v>813</v>
+      </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -5378,7 +5452,9 @@
       <c r="U38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V38" s="2"/>
+      <c r="V38" s="2" t="s">
+        <v>774</v>
+      </c>
       <c r="W38" s="2"/>
       <c r="X38" s="2" t="s">
         <v>36</v>
@@ -5398,7 +5474,7 @@
         <v>253</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>254</v>
+        <v>815</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>254</v>
@@ -5409,8 +5485,8 @@
       <c r="H39" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>255</v>
+      <c r="I39" s="6" t="s">
+        <v>814</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>256</v>
@@ -5460,7 +5536,7 @@
         <v>152</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>259</v>
+        <v>816</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>259</v>
@@ -5471,14 +5547,14 @@
       <c r="H40" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>260</v>
+      <c r="I40" s="6" t="s">
+        <v>817</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="K40" s="4" t="s">
-        <v>262</v>
+      <c r="K40" s="6" t="s">
+        <v>818</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>121</v>
@@ -5508,7 +5584,9 @@
       <c r="U40" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V40" s="2"/>
+      <c r="V40" s="2" t="s">
+        <v>774</v>
+      </c>
       <c r="W40" s="2"/>
       <c r="X40" s="2" t="s">
         <v>36</v>
@@ -10266,10 +10344,18 @@
     <hyperlink ref="K34" r:id="rId35" xr:uid="{CBA606A5-5B0F-43DF-B5C3-948742EEC118}"/>
     <hyperlink ref="I35" r:id="rId36" xr:uid="{C2310FEA-8ABA-4F25-8FF9-7D71210E3993}"/>
     <hyperlink ref="K35" r:id="rId37" xr:uid="{A9F3AB30-015F-4FAB-89B8-4EC9ACE9A77E}"/>
+    <hyperlink ref="K28" r:id="rId38" xr:uid="{54BD2142-FA34-477B-B70E-012D2533CCE1}"/>
+    <hyperlink ref="K36" r:id="rId39" xr:uid="{D4CA3E11-0AEF-405E-B890-D2EC6401988B}"/>
+    <hyperlink ref="I37" r:id="rId40" xr:uid="{BD44E353-0D73-44C3-BE51-49F863A80A43}"/>
+    <hyperlink ref="I38" r:id="rId41" xr:uid="{918311B4-1A9A-4B27-B1DF-49190DAD7DCB}"/>
+    <hyperlink ref="K38" r:id="rId42" xr:uid="{76CDEC4D-F3CC-4519-BE44-0FBF127BBF11}"/>
+    <hyperlink ref="I39" r:id="rId43" xr:uid="{FEEBBBC1-DAD3-4121-8B5D-9A86DD9BDF1F}"/>
+    <hyperlink ref="I40" r:id="rId44" xr:uid="{F77F7695-606D-41C9-909B-FC7D1F9D707B}"/>
+    <hyperlink ref="K40" r:id="rId45" xr:uid="{11323039-78C9-4934-853C-F9B51943B5D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId38"/>
+    <tablePart r:id="rId46"/>
   </tableParts>
 </worksheet>
 </file>

--- a/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
+++ b/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="R49d373928ea34840"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="R2e64559ab4d14d14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="Rd32e4cf610d043b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="R99162c98ed094bdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="R97337de1f01c483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="Rfbe00e9329484c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="Rc866f7ea6e4443b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="Rdb3eb34c0d124b56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="R2bb154708bb84831"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="R9a6d50c6efba4d4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4046,12 +4046,14 @@
       <x:c r="U19" s="2" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="V19" s="2" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="W19" s="2"/>
-      <x:c r="X19" s="2" t="s">
-        <x:v>36</x:v>
+      <x:c r="V19" s="2" t="str">
+        <x:v>跳过-无全院官方目录入口</x:v>
+      </x:c>
+      <x:c r="W19" s="2" t="str">
+        <x:v>两URL=芳村急诊1人、集团1人（无芳村）；院区200+，18人非全院；未采集/未写总表；全院目录后复排。</x:v>
+      </x:c>
+      <x:c r="X19" s="2" t="str">
+        <x:v>2026-08-12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
@@ -10066,55 +10068,55 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R316838eb524b49ed"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R1ca4ed07b0f74aaf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="Rf9d0edd8f7c24643"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R74965ece0f85480a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="Rd25944e367a94349"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="Rb1cd3b554d8044ab"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="R6c629b99a0814964"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="R835126c6650a4f38"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="R9b1a2c365d7947b5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R1f6dd2ca729b4bdb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="Rbd341694943349fe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R06bebf0dc42e4a4c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R28983e3a0cbc479c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R202652a4d40f4ddb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R38cf907f5a404aa8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="Rbfce05d6658f47f7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R6c16c8a4a09d4c6a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="R4fd9f38bc2fc47d9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R2817a1095d0e407e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R95e0166675354db6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="Rf858e119d50f4346"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="R6d24999fd2c64c7a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="R59208fd2fb16417c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="Rbc29d9aba4d04252"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="R949fc803423f4fbc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="R59a0a70412274464"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R3da6309250884d71"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="R7e5fd2f8a8924cad"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R0318dc724767441b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R6a73bd3739194eef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="Rf200c3671b264636"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="R63a2b4e815d04944"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R275e6cc2f2ed4552"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R4c1457d09d0e4dfd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="Rf4752c87ae9f46ff"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="Rb57dee9bbdfc4f49"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="R02c1fe92b7ec44a6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R26452fa3e66b4d81"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="R27320e242863491c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="Ra47b14f6946e45e9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="Rb9b70c9437b64c86"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R601daeb91cda4d34"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="R2865e1ec7a2c4e74"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="R6d6d2b2a57784afc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R733b894ddb4b4b06"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R677b9792ecbb4628"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="Rca596f49f2114c3e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="R9a959bfdd5184d3f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="Rcf0bd81adf8441ba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="R7c324eb12c6b4500"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R9af0fc2d712b4696"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="Rcd68994248d44602"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="Rdada0108f1b14bf1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="R301791c03cb14cc3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R429fcafab0694590"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="Rf5938269171546a1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="Rd4ae9d3adf0440bd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R4fd060fdb3d04133"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R5e129882c77f4993"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="Rc6d3de267c7b4a95"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="R561f8e2967bf4ce9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R5a7c8d77a55a4528"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="Rec43899055514aba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R158d8b523f204911"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R5e145ac87b584fda"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R62690551a5be43ae"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="R4cded82bb0094c39"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Rdc606b4c78ce4849"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="Re0fdf24ad8f14c52"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Ra7dc41f509ce49a9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="R1cf2ded07d5e46e6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Rd6da9995e13941cf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="Red2de00e44f64abd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R7d5c7350f33d4f18"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R149ba87370f34f9c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R5cb89d6b10f544cd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="R40ce36ba29154228"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R60b9b99504fe461b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Ra41ee7ac1ad04d33"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="R894ee2dda8954561"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R4882b0870369433a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="R2bf8727aa1a444fb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="Ra2da2a19b4ed4050"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Rb02df562848249b8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="R05254e76458a48b2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="Rda1dff60cde64812"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R88fab0e2ccb54d98"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="Rcd68c2e5163340ab"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="Racf881a6519340ea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="Rcd04d9be988b45e3"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R761825f8873f4969"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5b1d460238f493c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10393,7 +10395,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59bf6e7277304d93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9767b471b5b4057"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13060,7 +13062,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e73fdc73a0d4fc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a94d0391e624cf4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13116,7 +13118,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb30715261c54b6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re07780da93134424"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13188,7 +13190,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02ca08b7d42e4a16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb95683dfe12e4190"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
+++ b/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="Rfbe00e9329484c48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="Rc866f7ea6e4443b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="Rdb3eb34c0d124b56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="R2bb154708bb84831"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="R9a6d50c6efba4d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="R9d6c026564994f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="R965122bc7d9243da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="Rc0fee14ec9894c1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="R46022a833cac4d21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="Rc7f4f802f54e4f24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5102,7 +5102,7 @@
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="42" customHeight="1">
+    <x:row r="37" ht="60" customHeight="1">
       <x:c r="A37" s="2" t="s">
         <x:v>263</x:v>
       </x:c>
@@ -5150,16 +5150,20 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="S37" s="2"/>
-      <x:c r="T37" s="2"/>
-      <x:c r="U37" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="V37" s="2" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="W37" s="2"/>
-      <x:c r="X37" s="2" t="s">
-        <x:v>36</x:v>
+      <x:c r="T37" s="2" t="str">
+        <x:v>官网首页与 Issue #29 指定医生目录常规 GET 均返回 HTTP 403；响应页面标题为“您的访问请求可能对网站造成安全威胁，请求已被阻断。”未取得真实页面。禁止绕过站点安全拦截。</x:v>
+      </x:c>
+      <x:c r="U37" s="2" t="str">
+        <x:v>跳过本院；不绕过访问拦截；等待 owner 审计 Issue #29</x:v>
+      </x:c>
+      <x:c r="V37" s="2" t="str">
+        <x:v>跳过-访问拦截</x:v>
+      </x:c>
+      <x:c r="W37" s="2" t="str">
+        <x:v>2026-08-13 Codex 按 Issue #29 预先裁决执行：仅普通公开 HTTP GET，无挑战应答、验证码处理、浏览器指纹模拟、代理或第三方来源。未运行采集器，未写入总底表。证据见 Issue #29、WAF 报告与 ADR。</x:v>
+      </x:c>
+      <x:c r="X37" s="2" t="str">
+        <x:v>2026-08-13</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="42" customHeight="1">
@@ -10068,55 +10072,55 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R677b9792ecbb4628"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="Rca596f49f2114c3e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="R9a959bfdd5184d3f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="Rcf0bd81adf8441ba"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="R7c324eb12c6b4500"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R9af0fc2d712b4696"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="Rcd68994248d44602"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="Rdada0108f1b14bf1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="R301791c03cb14cc3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R429fcafab0694590"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="Rf5938269171546a1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="Rd4ae9d3adf0440bd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R4fd060fdb3d04133"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R5e129882c77f4993"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="Rc6d3de267c7b4a95"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="R561f8e2967bf4ce9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R5a7c8d77a55a4528"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="Rec43899055514aba"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R158d8b523f204911"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R5e145ac87b584fda"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R62690551a5be43ae"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="R4cded82bb0094c39"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Rdc606b4c78ce4849"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="Re0fdf24ad8f14c52"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Ra7dc41f509ce49a9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="R1cf2ded07d5e46e6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Rd6da9995e13941cf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="Red2de00e44f64abd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R7d5c7350f33d4f18"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R149ba87370f34f9c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R5cb89d6b10f544cd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="R40ce36ba29154228"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R60b9b99504fe461b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Ra41ee7ac1ad04d33"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="R894ee2dda8954561"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R4882b0870369433a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="R2bf8727aa1a444fb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="Ra2da2a19b4ed4050"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Rb02df562848249b8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="R05254e76458a48b2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="Rda1dff60cde64812"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R88fab0e2ccb54d98"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="Rcd68c2e5163340ab"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="Racf881a6519340ea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="Rcd04d9be988b45e3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R4044a9c4e1ca468f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="Rb49900af14fd4721"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="Re8e0ff779ec24c16"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R353f4bccb6024cc3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="R9846b63c6eda411d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R33d26b88042a4679"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="Rb6324b838d914b02"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="Rbf0347b6adf4414e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="Rdc9d0621a17e4518"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="Rf1e32b74b8444a1f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="R38a889087d434af6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R769dc5414bf3499b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R9c96705701624c24"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="Rf7e1fb82725c444d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R60b6322216834f36"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="R866ff2830b5d4609"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R6bab108250a94705"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="Rb6309be3c9944186"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R2753fe086e09493c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="Rff88087034ea4d12"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R44f3cf1d3753484d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="Rd5389feb365842c9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Rbf1da644c1ae4699"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="R630dfff9ca1b4ee9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rdc0cf2ea6fb94b06"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="R51640ccf1acb4c3b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R59da4011c31e43b5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="R81668c0658804770"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R6224f69f4f314b3d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R1a06ed87f19140a1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R4eb9d5aab98d4a9d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="R9ac7a414a102412c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="Re9c33e1537a54328"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R6542ad29523c4e32"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="Rf3c93764109b45a4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R4a92ff74d39b4177"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="Rf3cb103f7b004ff3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="Ra5170a45ba7c40e8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="R0723497e14a04efb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="R53f197e4aec847a0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="R4c447dfd30894689"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="Rabe730b8c8b94942"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="Ra459bebbe6584d03"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="R1e2afbb3e6224125"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="Rcdc12b352a924608"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5b1d460238f493c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7f17bc62c56470c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10395,7 +10399,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9767b471b5b4057"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ac9af835ff24b83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11239,7 +11243,7 @@
       <x:c r="H36" s="2"/>
       <x:c r="I36" s="2"/>
     </x:row>
-    <x:row r="37" ht="16.5">
+    <x:row r="37" ht="60" customHeight="1">
       <x:c r="A37" s="2" t="s">
         <x:v>25</x:v>
       </x:c>
@@ -11254,11 +11258,15 @@
       <x:c r="F37" s="2" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G37" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H37" s="2"/>
-      <x:c r="I37" s="2"/>
+      <x:c r="G37" s="2" t="str">
+        <x:v>跳过本院；不绕过访问拦截；等待 owner 审计 Issue #29</x:v>
+      </x:c>
+      <x:c r="H37" s="2" t="str">
+        <x:v>跳过-访问拦截</x:v>
+      </x:c>
+      <x:c r="I37" s="2" t="str">
+        <x:v>官网首页与医生目录均 HTTP 403，页面提示访问请求可能造成安全威胁并已阻断；仅普通 GET，未取得真实页面，未运行采集器，未写入总底表。</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="16.5">
       <x:c r="A38" s="2" t="s">
@@ -13062,7 +13070,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a94d0391e624cf4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0474317d56504f54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13118,7 +13126,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re07780da93134424"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc374a3a6b4554bc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13190,7 +13198,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb95683dfe12e4190"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8beac2faabb44a81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
+++ b/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="R9d6c026564994f5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="R965122bc7d9243da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="Rc0fee14ec9894c1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="R46022a833cac4d21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="Rc7f4f802f54e4f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="Rf35e6269431e4304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="Rcc579bebcdd446b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="Rbd5eb8b909bc47a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="R737b89720af04288"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="R40e26bf4548c4930"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3376,8 +3376,8 @@
       <x:c r="U9" s="2" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="V9" s="2" t="s">
-        <x:v>66</x:v>
+      <x:c r="V9" s="2" t="str">
+        <x:v>跳过-与序号7同源目录已全量入库</x:v>
       </x:c>
       <x:c r="W9" s="2"/>
       <x:c r="X9" s="2" t="s">
@@ -10072,55 +10072,55 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R4044a9c4e1ca468f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="Rb49900af14fd4721"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="Re8e0ff779ec24c16"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R353f4bccb6024cc3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="R9846b63c6eda411d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R33d26b88042a4679"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="Rb6324b838d914b02"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="Rbf0347b6adf4414e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="Rdc9d0621a17e4518"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="Rf1e32b74b8444a1f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="R38a889087d434af6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R769dc5414bf3499b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R9c96705701624c24"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="Rf7e1fb82725c444d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R60b6322216834f36"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="R866ff2830b5d4609"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="R6bab108250a94705"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="Rb6309be3c9944186"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R2753fe086e09493c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="Rff88087034ea4d12"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R44f3cf1d3753484d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="Rd5389feb365842c9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Rbf1da644c1ae4699"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="R630dfff9ca1b4ee9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rdc0cf2ea6fb94b06"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="R51640ccf1acb4c3b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R59da4011c31e43b5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="R81668c0658804770"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R6224f69f4f314b3d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R1a06ed87f19140a1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R4eb9d5aab98d4a9d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="R9ac7a414a102412c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="Re9c33e1537a54328"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R6542ad29523c4e32"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="Rf3c93764109b45a4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R4a92ff74d39b4177"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="Rf3cb103f7b004ff3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="Ra5170a45ba7c40e8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="R0723497e14a04efb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="R53f197e4aec847a0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="R4c447dfd30894689"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="Rabe730b8c8b94942"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="Ra459bebbe6584d03"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="R1e2afbb3e6224125"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="Rcdc12b352a924608"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R5c5cb511f9174bb5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R816b2b1b49af4372"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="R2fbc8c34401d4696"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R70515154b72c484d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="Rd6961ada84a24cab"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="Ra8bfc8fad18d4af2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="R7029fdb0c7034d46"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="R2d84657936884abe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="Rbdbdf2f19b1a4919"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R54177e6efed64abe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="R75b3b73fd9d242b4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R4d94383b46524367"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R3bc2b2c67d1341c6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R121519b2079144bc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R2bb716764146401f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="R725e7f3d53ed4142"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="Rffe98eb621774859"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="R533fe849af00449a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R2f58a6e5452444c6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R9f69ee3ac01f43b9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="Rb028a6fbd72d4d28"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="Rcc8098f036ec40d3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Rfd0e05f16e10407d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="Rb5f1cff263eb4ef7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="R4b18753b1a2c4e90"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="Rd9e45dbc3e7749df"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Re0f8e023cd2e4417"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="Rb6a438b94f724e6c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R5a20f01e46b640f5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R0a0ec7c60d6c4436"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="Ra192084f6e484ba9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="R0ee6307f9a3d44f5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R43209ec63c0b4154"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R4db21bde1e3a400b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="Rfd9dc3c6512b43ec"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R7910902f71ae4563"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="R4a12cff2ac7c4cc7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R5a2d0f96c539415f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Rc1cb169b2ed7465f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="Rb5fb01bbe7474d41"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="R2619a68161764b3b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="Re09fd8bd35db4710"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="Rb055ebba446948fc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="Rfd4901d499ba46e5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R5ee1bd6c8a2c4ee9"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7f17bc62c56470c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R755524f7b0964f8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10399,7 +10399,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ac9af835ff24b83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e420795aea544db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13070,7 +13070,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0474317d56504f54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R606f5c685f4744a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13126,7 +13126,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc374a3a6b4554bc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1911f1256b474a75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13198,7 +13198,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8beac2faabb44a81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R730f1bbf038a4738"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
+++ b/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="Rf35e6269431e4304"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="Rcc579bebcdd446b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="Rbd5eb8b909bc47a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="R737b89720af04288"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="R40e26bf4548c4930"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="R2ab4198e6161431f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="R7f0d2d9028f94b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="Rdccb00b49d3a4bce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="R4f2881f123a44714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="R334e36c6f8f54623"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -326,9 +326,6 @@
     <x:t xml:space="preserve">南方医科大学口腔医院</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">https://www.smukqyy.cn/section/364</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">医生目录</x:t>
   </x:si>
   <x:si>
@@ -366,9 +363,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">南方医科大学皮肤病医院,广东省皮肤病医院,广东省皮肤性病防治中心,中国麻风防治研究中心官网主页</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.gdskin.com/Showclass.aspx?id=901</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">南方医科大学皮肤病医院 官方网站 官网</x:t>
@@ -3454,7 +3448,7 @@
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="42" customHeight="1">
+    <x:row r="11" ht="120" hidden="0" customHeight="1">
       <x:c r="A11" s="2" t="s">
         <x:v>100</x:v>
       </x:c>
@@ -3485,11 +3479,19 @@
       <x:c r="J11" s="2" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="K11" s="6" t="s">
+      <x:c r="K11" s="6" t="str">
+        <x:v>https://www.smukqyy.cn/section/341
+https://www.smukqyy.cn/section/342
+https://www.smukqyy.cn/section/434
+https://www.smukqyy.cn/section/343
+https://www.smukqyy.cn/section/385
+https://www.smukqyy.cn/section/384
+https://www.smukqyy.cn/section/386
+https://www.smukqyy.cn/section/431
+https://www.smukqyy.cn/section/504</x:v>
+      </x:c>
+      <x:c r="L11" s="2" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="L11" s="2" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="M11" s="2" t="s">
         <x:v>57</x:v>
@@ -3507,13 +3509,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R11" s="4" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="S11" s="2" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="S11" s="2" t="s">
+      <x:c r="T11" s="2" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="T11" s="2" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="U11" s="2" t="s">
         <x:v>65</x:v>
@@ -3521,14 +3523,16 @@
       <x:c r="V11" s="2" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="W11" s="2"/>
-      <x:c r="X11" s="2" t="s">
-        <x:v>36</x:v>
+      <x:c r="W11" s="2" t="str">
+        <x:v>2026-08-11 owner PR #6 范围裁决：原 /section/364 属总院单科室，已更正为海珠广场院区 9 个官方科室入口；范围不含其他院区。</x:v>
+      </x:c>
+      <x:c r="X11" s="2" t="str">
+        <x:v>2026-08-16</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
         <x:v>24</x:v>
@@ -3540,10 +3544,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F12" s="2" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="F12" s="2" t="s">
-        <x:v>111</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
         <x:v>29</x:v>
@@ -3567,7 +3571,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R12" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="S12" s="2"/>
       <x:c r="T12" s="2"/>
@@ -3580,9 +3584,9 @@
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="42" customHeight="1">
+    <x:row r="13" ht="132" hidden="0" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
         <x:v>24</x:v>
@@ -3594,10 +3598,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F13" s="2" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="F13" s="2" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
         <x:v>29</x:v>
@@ -3606,16 +3610,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I13" s="4" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="J13" s="2" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="J13" s="2" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="K13" s="6" t="s">
-        <x:v>118</x:v>
+      <x:c r="K13" s="6" t="str">
+        <x:v>https://www.gdskin.com/Showclass.aspx?id=901
+https://www.gdskin.com/Showclass.aspx?id=902
+https://www.gdskin.com/Showclass.aspx?id=906
+https://www.gdskin.com/Showclass.aspx?id=910
+https://www.gdskin.com/Showclass.aspx?id=913
+https://www.gdskin.com/Showclass.aspx?id=915
+https://www.gdskin.com/Showclass.aspx?id=917
+https://www.gdskin.com/Showclass.aspx?id=921
+https://www.gdskin.com/ShowClass.aspx?id=922
+https://www.gdskin.com/ShowClass.aspx?id=924</x:v>
       </x:c>
       <x:c r="L13" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M13" s="2" t="s">
         <x:v>57</x:v>
@@ -3633,13 +3646,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R13" s="4" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="S13" s="2" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="T13" s="2" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="S13" s="2" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="T13" s="2" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="U13" s="2" t="s">
         <x:v>65</x:v>
@@ -3647,14 +3660,16 @@
       <x:c r="V13" s="2" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="W13" s="2"/>
-      <x:c r="X13" s="2" t="s">
-        <x:v>36</x:v>
+      <x:c r="W13" s="2" t="str">
+        <x:v>2026-08-11 owner Issue #7 / PR #8 核验：原单入口 901 为专家团队导航入口，已更正为 10 个官方分类入口；924 零记录保留留痕。</x:v>
+      </x:c>
+      <x:c r="X13" s="2" t="str">
+        <x:v>2026-08-16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
         <x:v>24</x:v>
@@ -3666,10 +3681,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E14" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F14" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G14" s="2" t="s">
         <x:v>29</x:v>
@@ -3678,16 +3693,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I14" s="6" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="J14" s="2" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="K14" s="6" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="L14" s="2" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="J14" s="2" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="K14" s="6" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="L14" s="2" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="M14" s="2" t="s">
         <x:v>57</x:v>
@@ -3705,10 +3720,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R14" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="S14" s="2" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="T14" s="2" t="str">
         <x:v>官网首页常规 GET 返回 HTTP 412；Issue 指定入口常规 GET 返回 HTTP 405；两者 Server 均为 CT2-WAAP，未取得真实页面。禁止绕过反爬。</x:v>
@@ -3728,7 +3743,7 @@
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
         <x:v>24</x:v>
@@ -3737,13 +3752,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E15" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F15" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
         <x:v>29</x:v>
@@ -3752,13 +3767,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I15" s="6" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J15" s="2" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="K15" s="6" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="K15" s="6" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="L15" s="2" t="s">
         <x:v>56</x:v>
@@ -3779,10 +3794,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R15" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="S15" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="T15" s="2"/>
       <x:c r="U15" s="2" t="s">
@@ -3798,7 +3813,7 @@
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
         <x:v>24</x:v>
@@ -3810,10 +3825,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
         <x:v>29</x:v>
@@ -3822,13 +3837,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I16" s="4" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="J16" s="2" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="K16" s="6" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="J16" s="2" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="K16" s="6" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="L16" s="2" t="s">
         <x:v>56</x:v>
@@ -3849,10 +3864,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R16" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="S16" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="T16" s="2" t="s">
         <x:v>64</x:v>
@@ -3870,7 +3885,7 @@
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
         <x:v>24</x:v>
@@ -3882,10 +3897,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
         <x:v>29</x:v>
@@ -3894,33 +3909,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I17" s="4" t="s">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="J17" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K17" s="4"/>
       <x:c r="L17" s="2"/>
       <x:c r="M17" s="2"/>
       <x:c r="N17" s="2"/>
       <x:c r="O17" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P17" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q17" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="R17" s="4" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="S17" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="T17" s="2"/>
       <x:c r="U17" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V17" s="2"/>
       <x:c r="W17" s="2"/>
@@ -3930,7 +3945,7 @@
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="2" t="s">
-        <x:v>154</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
         <x:v>24</x:v>
@@ -3942,10 +3957,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>155</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>155</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
         <x:v>29</x:v>
@@ -3969,7 +3984,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R18" s="4" t="s">
-        <x:v>156</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="S18" s="2"/>
       <x:c r="T18" s="2"/>
@@ -3984,7 +3999,7 @@
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="2" t="s">
-        <x:v>157</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
         <x:v>24</x:v>
@@ -3993,13 +4008,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F19" s="2" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="E19" s="2" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F19" s="2" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
         <x:v>29</x:v>
@@ -4008,13 +4023,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I19" s="4" t="s">
-        <x:v>161</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J19" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K19" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="L19" s="2" t="s">
         <x:v>56</x:v>
@@ -4032,16 +4047,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q19" s="2" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="R19" s="4" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="S19" s="2" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="R19" s="4" t="s">
+      <x:c r="T19" s="2" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="S19" s="2" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="T19" s="2" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="U19" s="2" t="s">
         <x:v>65</x:v>
@@ -4058,7 +4073,7 @@
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="2" t="s">
-        <x:v>167</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
         <x:v>24</x:v>
@@ -4070,10 +4085,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E20" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
         <x:v>29</x:v>
@@ -4082,11 +4097,11 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I20" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="J20" s="2"/>
       <x:c r="K20" s="6" t="s">
-        <x:v>171</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="L20" s="2"/>
       <x:c r="M20" s="2"/>
@@ -4101,7 +4116,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R20" s="4" t="s">
-        <x:v>172</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="S20" s="2"/>
       <x:c r="T20" s="2"/>
@@ -4118,7 +4133,7 @@
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
         <x:v>24</x:v>
@@ -4130,10 +4145,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E21" s="2" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
         <x:v>29</x:v>
@@ -4157,7 +4172,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R21" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="S21" s="2"/>
       <x:c r="T21" s="2" t="s">
@@ -4174,7 +4189,7 @@
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="2" t="s">
-        <x:v>176</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
         <x:v>24</x:v>
@@ -4183,13 +4198,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E22" s="2" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F22" s="2" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
         <x:v>29</x:v>
@@ -4198,11 +4213,11 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I22" s="6" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J22" s="2"/>
       <x:c r="K22" s="6" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="L22" s="2"/>
       <x:c r="M22" s="2"/>
@@ -4217,7 +4232,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R22" s="4" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="S22" s="2"/>
       <x:c r="T22" s="2"/>
@@ -4234,7 +4249,7 @@
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="2" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
         <x:v>24</x:v>
@@ -4246,10 +4261,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
         <x:v>29</x:v>
@@ -4258,16 +4273,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I23" s="6" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="J23" s="2" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="K23" s="6" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="J23" s="2" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="K23" s="6" t="s">
-        <x:v>186</x:v>
-      </x:c>
       <x:c r="L23" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M23" s="2" t="s">
         <x:v>57</x:v>
@@ -4282,16 +4297,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q23" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R23" s="4" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="S23" s="2" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="T23" s="2" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="S23" s="2" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="T23" s="2" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="U23" s="2" t="s">
         <x:v>65</x:v>
@@ -4306,7 +4321,7 @@
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="2" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
         <x:v>24</x:v>
@@ -4318,10 +4333,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E24" s="2" t="s">
-        <x:v>191</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F24" s="2" t="s">
-        <x:v>192</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
         <x:v>29</x:v>
@@ -4330,11 +4345,11 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I24" s="6" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J24" s="2"/>
       <x:c r="K24" s="6" t="s">
-        <x:v>194</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="L24" s="2"/>
       <x:c r="M24" s="2"/>
@@ -4349,7 +4364,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R24" s="4" t="s">
-        <x:v>195</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="S24" s="2"/>
       <x:c r="T24" s="2"/>
@@ -4366,7 +4381,7 @@
     </x:row>
     <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="2" t="s">
-        <x:v>196</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
         <x:v>24</x:v>
@@ -4378,10 +4393,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F25" s="2" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
         <x:v>29</x:v>
@@ -4390,11 +4405,11 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I25" s="6" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="J25" s="2"/>
       <x:c r="K25" s="6" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="L25" s="2"/>
       <x:c r="M25" s="2"/>
@@ -4409,10 +4424,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R25" s="4" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="S25" s="2" t="s">
-        <x:v>201</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="T25" s="2"/>
       <x:c r="U25" s="2" t="s">
@@ -4428,7 +4443,7 @@
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="2" t="s">
-        <x:v>202</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
         <x:v>24</x:v>
@@ -4437,13 +4452,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D26" s="2" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E26" s="2" t="s">
-        <x:v>203</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F26" s="2" t="s">
-        <x:v>203</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
         <x:v>29</x:v>
@@ -4452,11 +4467,11 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I26" s="6" t="s">
-        <x:v>204</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="J26" s="2"/>
       <x:c r="K26" s="6" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="L26" s="2"/>
       <x:c r="M26" s="2"/>
@@ -4471,7 +4486,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R26" s="4" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="S26" s="2"/>
       <x:c r="T26" s="2"/>
@@ -4488,7 +4503,7 @@
     </x:row>
     <x:row r="27" ht="42" customHeight="1">
       <x:c r="A27" s="2" t="s">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
         <x:v>24</x:v>
@@ -4500,16 +4515,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E27" s="2" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F27" s="2" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H27" s="2" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="I27" s="4"/>
       <x:c r="J27" s="2"/>
@@ -4527,7 +4542,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R27" s="4" t="s">
-        <x:v>210</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="S27" s="2"/>
       <x:c r="T27" s="2" t="s">
@@ -4542,9 +4557,9 @@
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="42" customHeight="1">
+    <x:row r="28" ht="72" hidden="0" customHeight="1">
       <x:c r="A28" s="2" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
         <x:v>24</x:v>
@@ -4556,10 +4571,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E28" s="2" t="s">
-        <x:v>212</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F28" s="2" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G28" s="2" t="s">
         <x:v>29</x:v>
@@ -4568,11 +4583,11 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I28" s="4" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="J28" s="2"/>
       <x:c r="K28" s="6" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="L28" s="2"/>
       <x:c r="M28" s="2"/>
@@ -4587,24 +4602,26 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R28" s="4" t="s">
-        <x:v>216</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="S28" s="2"/>
       <x:c r="T28" s="2"/>
       <x:c r="U28" s="2" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="V28" s="2" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="W28" s="2"/>
-      <x:c r="X28" s="2" t="s">
-        <x:v>36</x:v>
+      <x:c r="V28" s="2" t="str">
+        <x:v>跳过-入口不可达/已废弃</x:v>
+      </x:c>
+      <x:c r="W28" s="2" t="str">
+        <x:v>2026-08-15 owner PR #52 裁决：官网首页现场 404→403、指定医生目录两次 404；请求无重定向、未绕过、未采集未写总表。管理员补充有效官方入口后可复排。</x:v>
+      </x:c>
+      <x:c r="X28" s="2" t="str">
+        <x:v>2026-08-16</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
       <x:c r="A29" s="2" t="s">
-        <x:v>217</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
         <x:v>24</x:v>
@@ -4613,13 +4630,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E29" s="2" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F29" s="2" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G29" s="2" t="s">
         <x:v>29</x:v>
@@ -4643,7 +4660,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R29" s="4" t="s">
-        <x:v>219</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="S29" s="2"/>
       <x:c r="T29" s="2" t="s">
@@ -4660,7 +4677,7 @@
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
       <x:c r="A30" s="2" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
         <x:v>24</x:v>
@@ -4669,13 +4686,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E30" s="2" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F30" s="2" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="E30" s="2" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F30" s="2" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="G30" s="2" t="s">
         <x:v>29</x:v>
@@ -4699,10 +4716,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R30" s="4" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="S30" s="2" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="T30" s="2"/>
       <x:c r="U30" s="2" t="s">
@@ -4716,7 +4733,7 @@
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
       <x:c r="A31" s="2" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
         <x:v>24</x:v>
@@ -4728,10 +4745,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E31" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F31" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="G31" s="2" t="s">
         <x:v>29</x:v>
@@ -4740,33 +4757,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I31" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="J31" s="2" t="s">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="K31" s="4"/>
       <x:c r="L31" s="2"/>
       <x:c r="M31" s="2"/>
       <x:c r="N31" s="2"/>
       <x:c r="O31" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P31" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q31" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R31" s="4" t="s">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="S31" s="2" t="s">
-        <x:v>231</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="T31" s="2"/>
       <x:c r="U31" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V31" s="2"/>
       <x:c r="W31" s="2"/>
@@ -4776,7 +4793,7 @@
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="2" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
         <x:v>24</x:v>
@@ -4788,10 +4805,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E32" s="2" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F32" s="2" t="s">
-        <x:v>234</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G32" s="2" t="s">
         <x:v>29</x:v>
@@ -4815,7 +4832,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R32" s="4" t="s">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="S32" s="2"/>
       <x:c r="T32" s="2" t="s">
@@ -4832,7 +4849,7 @@
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="2" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
         <x:v>24</x:v>
@@ -4844,10 +4861,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E33" s="2" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="F33" s="2" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G33" s="2" t="s">
         <x:v>29</x:v>
@@ -4871,7 +4888,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R33" s="4" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="S33" s="2"/>
       <x:c r="T33" s="2" t="s">
@@ -4888,7 +4905,7 @@
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
       <x:c r="A34" s="2" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B34" s="2" t="s">
         <x:v>24</x:v>
@@ -4897,13 +4914,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E34" s="2" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F34" s="2" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="G34" s="2" t="s">
         <x:v>29</x:v>
@@ -4912,13 +4929,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I34" s="4" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="J34" s="2" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="K34" s="6" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="J34" s="2" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="K34" s="6" t="s">
-        <x:v>244</x:v>
       </x:c>
       <x:c r="L34" s="2" t="s">
         <x:v>56</x:v>
@@ -4939,10 +4956,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R34" s="4" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="S34" s="2" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="T34" s="2" t="s">
         <x:v>64</x:v>
@@ -4960,7 +4977,7 @@
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="2" t="s">
-        <x:v>247</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B35" s="2" t="s">
         <x:v>24</x:v>
@@ -4972,10 +4989,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E35" s="2" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="F35" s="2" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G35" s="2" t="s">
         <x:v>29</x:v>
@@ -4984,13 +5001,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I35" s="6" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="J35" s="2" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="K35" s="6" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="J35" s="2" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="K35" s="6" t="s">
-        <x:v>251</x:v>
       </x:c>
       <x:c r="L35" s="2" t="s">
         <x:v>56</x:v>
@@ -5011,13 +5028,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R35" s="4" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="S35" s="2" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="T35" s="2" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="S35" s="2" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="T35" s="2" t="s">
-        <x:v>254</x:v>
       </x:c>
       <x:c r="U35" s="2" t="s">
         <x:v>65</x:v>
@@ -5032,7 +5049,7 @@
     </x:row>
     <x:row r="36" ht="42" customHeight="1">
       <x:c r="A36" s="2" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B36" s="2" t="s">
         <x:v>24</x:v>
@@ -5041,13 +5058,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E36" s="2" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F36" s="2" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G36" s="2" t="s">
         <x:v>29</x:v>
@@ -5056,16 +5073,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I36" s="4" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="J36" s="2" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K36" s="6" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="J36" s="2" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="K36" s="6" t="s">
-        <x:v>259</x:v>
-      </x:c>
       <x:c r="L36" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M36" s="2" t="s">
         <x:v>57</x:v>
@@ -5083,13 +5100,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R36" s="4" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="S36" s="2" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="T36" s="2" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="S36" s="2" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="T36" s="2" t="s">
-        <x:v>262</x:v>
       </x:c>
       <x:c r="U36" s="2" t="s">
         <x:v>65</x:v>
@@ -5104,7 +5121,7 @@
     </x:row>
     <x:row r="37" ht="60" customHeight="1">
       <x:c r="A37" s="2" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B37" s="2" t="s">
         <x:v>24</x:v>
@@ -5116,10 +5133,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E37" s="2" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F37" s="2" t="s">
-        <x:v>265</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G37" s="2" t="s">
         <x:v>29</x:v>
@@ -5128,11 +5145,11 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I37" s="6" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="J37" s="2"/>
       <x:c r="K37" s="4" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="L37" s="2"/>
       <x:c r="M37" s="2"/>
@@ -5147,7 +5164,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R37" s="4" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="S37" s="2"/>
       <x:c r="T37" s="2" t="str">
@@ -5168,7 +5185,7 @@
     </x:row>
     <x:row r="38" ht="42" customHeight="1">
       <x:c r="A38" s="2" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
         <x:v>24</x:v>
@@ -5177,13 +5194,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D38" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E38" s="2" t="s">
-        <x:v>270</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="F38" s="2" t="s">
-        <x:v>270</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="G38" s="2" t="s">
         <x:v>29</x:v>
@@ -5192,11 +5209,11 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I38" s="6" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="J38" s="2"/>
       <x:c r="K38" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L38" s="2"/>
       <x:c r="M38" s="2"/>
@@ -5211,7 +5228,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R38" s="4" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="S38" s="2"/>
       <x:c r="T38" s="2"/>
@@ -5228,7 +5245,7 @@
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
       <x:c r="A39" s="2" t="s">
-        <x:v>274</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
         <x:v>24</x:v>
@@ -5237,13 +5254,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D39" s="2" t="s">
-        <x:v>275</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E39" s="2" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="F39" s="2" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="G39" s="2" t="s">
         <x:v>29</x:v>
@@ -5252,35 +5269,35 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I39" s="6" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="J39" s="2" t="s">
-        <x:v>278</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="K39" s="4"/>
       <x:c r="L39" s="2"/>
       <x:c r="M39" s="2"/>
       <x:c r="N39" s="2"/>
       <x:c r="O39" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P39" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q39" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R39" s="4" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="S39" s="2" t="s">
-        <x:v>279</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="T39" s="2" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="U39" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V39" s="2"/>
       <x:c r="W39" s="2"/>
@@ -5290,7 +5307,7 @@
     </x:row>
     <x:row r="40" ht="42" customHeight="1">
       <x:c r="A40" s="2" t="s">
-        <x:v>280</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B40" s="2" t="s">
         <x:v>24</x:v>
@@ -5299,13 +5316,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D40" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E40" s="2" t="s">
-        <x:v>281</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="F40" s="2" t="s">
-        <x:v>281</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="G40" s="2" t="s">
         <x:v>29</x:v>
@@ -5314,16 +5331,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I40" s="6" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="J40" s="2" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="K40" s="6" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="J40" s="2" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="K40" s="6" t="s">
-        <x:v>284</x:v>
-      </x:c>
       <x:c r="L40" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="M40" s="2" t="s">
         <x:v>57</x:v>
@@ -5338,13 +5355,13 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q40" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R40" s="4" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="S40" s="2" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="T40" s="2"/>
       <x:c r="U40" s="2" t="s">
@@ -5360,7 +5377,7 @@
     </x:row>
     <x:row r="41" ht="42" customHeight="1">
       <x:c r="A41" s="2" t="s">
-        <x:v>287</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B41" s="2" t="s">
         <x:v>24</x:v>
@@ -5369,13 +5386,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D41" s="2" t="s">
-        <x:v>275</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E41" s="2" t="s">
-        <x:v>288</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="F41" s="2" t="s">
-        <x:v>289</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="G41" s="2" t="s">
         <x:v>29</x:v>
@@ -5384,16 +5401,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I41" s="4" t="s">
-        <x:v>290</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="J41" s="2" t="s">
-        <x:v>288</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="K41" s="4" t="s">
-        <x:v>291</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="L41" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="M41" s="2" t="s">
         <x:v>57</x:v>
@@ -5411,10 +5428,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R41" s="4" t="s">
-        <x:v>292</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="S41" s="2" t="s">
-        <x:v>293</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="T41" s="2"/>
       <x:c r="U41" s="2" t="s">
@@ -5428,7 +5445,7 @@
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
       <x:c r="A42" s="2" t="s">
-        <x:v>294</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B42" s="2" t="s">
         <x:v>24</x:v>
@@ -5437,13 +5454,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D42" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E42" s="2" t="s">
-        <x:v>295</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F42" s="2" t="s">
-        <x:v>295</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G42" s="2" t="s">
         <x:v>29</x:v>
@@ -5467,7 +5484,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R42" s="4" t="s">
-        <x:v>296</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="S42" s="2"/>
       <x:c r="T42" s="2"/>
@@ -5482,7 +5499,7 @@
     </x:row>
     <x:row r="43" ht="42" customHeight="1">
       <x:c r="A43" s="2" t="s">
-        <x:v>297</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B43" s="2" t="s">
         <x:v>24</x:v>
@@ -5491,13 +5508,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D43" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E43" s="2" t="s">
-        <x:v>298</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F43" s="2" t="s">
-        <x:v>299</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G43" s="2" t="s">
         <x:v>29</x:v>
@@ -5506,37 +5523,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I43" s="4" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="J43" s="2" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K43" s="4" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="L43" s="2" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="J43" s="2" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="K43" s="4" t="s">
+      <x:c r="M43" s="2" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="L43" s="2" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="M43" s="2" t="s">
-        <x:v>303</x:v>
       </x:c>
       <x:c r="N43" s="2" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="O43" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="P43" s="2" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q43" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R43" s="4" t="s">
-        <x:v>305</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="S43" s="2" t="s">
-        <x:v>306</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="T43" s="2"/>
       <x:c r="U43" s="2" t="s">
@@ -5550,7 +5567,7 @@
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="2" t="s">
-        <x:v>307</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B44" s="2" t="s">
         <x:v>24</x:v>
@@ -5559,13 +5576,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D44" s="2" t="s">
-        <x:v>308</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E44" s="2" t="s">
-        <x:v>309</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F44" s="2" t="s">
-        <x:v>309</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="G44" s="2" t="s">
         <x:v>29</x:v>
@@ -5574,13 +5591,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I44" s="4" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="J44" s="2" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="K44" s="4" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="J44" s="2" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="K44" s="4" t="s">
-        <x:v>312</x:v>
       </x:c>
       <x:c r="L44" s="2" t="s">
         <x:v>56</x:v>
@@ -5598,16 +5615,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q44" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R44" s="4" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="S44" s="2" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="T44" s="2" t="s">
         <x:v>313</x:v>
-      </x:c>
-      <x:c r="S44" s="2" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="T44" s="2" t="s">
-        <x:v>315</x:v>
       </x:c>
       <x:c r="U44" s="2" t="s">
         <x:v>65</x:v>
@@ -5620,7 +5637,7 @@
     </x:row>
     <x:row r="45" ht="42" customHeight="1">
       <x:c r="A45" s="2" t="s">
-        <x:v>316</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B45" s="2" t="s">
         <x:v>24</x:v>
@@ -5629,13 +5646,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D45" s="2" t="s">
-        <x:v>308</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E45" s="2" t="s">
-        <x:v>317</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F45" s="2" t="s">
-        <x:v>318</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="G45" s="2" t="s">
         <x:v>29</x:v>
@@ -5644,13 +5661,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I45" s="4" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="J45" s="2" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="K45" s="4" t="s">
         <x:v>319</x:v>
-      </x:c>
-      <x:c r="J45" s="2" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="K45" s="4" t="s">
-        <x:v>321</x:v>
       </x:c>
       <x:c r="L45" s="2" t="s">
         <x:v>56</x:v>
@@ -5671,10 +5688,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R45" s="4" t="s">
-        <x:v>322</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="S45" s="2" t="s">
-        <x:v>323</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="T45" s="2"/>
       <x:c r="U45" s="2" t="s">
@@ -5688,7 +5705,7 @@
     </x:row>
     <x:row r="46" ht="42" customHeight="1">
       <x:c r="A46" s="2" t="s">
-        <x:v>324</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B46" s="2" t="s">
         <x:v>24</x:v>
@@ -5700,10 +5717,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E46" s="2" t="s">
-        <x:v>325</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="F46" s="2" t="s">
-        <x:v>325</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="G46" s="2" t="s">
         <x:v>29</x:v>
@@ -5712,16 +5729,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I46" s="4" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="J46" s="2" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="K46" s="4" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="J46" s="2" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="K46" s="4" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="L46" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M46" s="2" t="s">
         <x:v>57</x:v>
@@ -5736,16 +5753,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q46" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R46" s="4" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="S46" s="2" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="T46" s="2" t="s">
         <x:v>329</x:v>
-      </x:c>
-      <x:c r="S46" s="2" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="T46" s="2" t="s">
-        <x:v>331</x:v>
       </x:c>
       <x:c r="U46" s="2" t="s">
         <x:v>65</x:v>
@@ -5758,7 +5775,7 @@
     </x:row>
     <x:row r="47" ht="42" customHeight="1">
       <x:c r="A47" s="2" t="s">
-        <x:v>332</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B47" s="2" t="s">
         <x:v>24</x:v>
@@ -5767,13 +5784,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D47" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E47" s="2" t="s">
-        <x:v>333</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F47" s="2" t="s">
-        <x:v>334</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="G47" s="2" t="s">
         <x:v>29</x:v>
@@ -5797,7 +5814,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R47" s="4" t="s">
-        <x:v>335</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="S47" s="2"/>
       <x:c r="T47" s="2" t="s">
@@ -5814,7 +5831,7 @@
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
       <x:c r="A48" s="2" t="s">
-        <x:v>336</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B48" s="2" t="s">
         <x:v>24</x:v>
@@ -5826,10 +5843,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E48" s="2" t="s">
-        <x:v>337</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F48" s="2" t="s">
-        <x:v>338</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="G48" s="2" t="s">
         <x:v>29</x:v>
@@ -5853,7 +5870,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R48" s="4" t="s">
-        <x:v>339</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="S48" s="2"/>
       <x:c r="T48" s="2"/>
@@ -5868,7 +5885,7 @@
     </x:row>
     <x:row r="49" ht="42" customHeight="1">
       <x:c r="A49" s="2" t="s">
-        <x:v>340</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B49" s="2" t="s">
         <x:v>24</x:v>
@@ -5880,10 +5897,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E49" s="2" t="s">
-        <x:v>341</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F49" s="2" t="s">
-        <x:v>341</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="G49" s="2" t="s">
         <x:v>29</x:v>
@@ -5907,7 +5924,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R49" s="4" t="s">
-        <x:v>342</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="S49" s="2"/>
       <x:c r="T49" s="2" t="s">
@@ -5924,7 +5941,7 @@
     </x:row>
     <x:row r="50" ht="42" customHeight="1">
       <x:c r="A50" s="2" t="s">
-        <x:v>343</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B50" s="2" t="s">
         <x:v>24</x:v>
@@ -5933,13 +5950,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D50" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E50" s="2" t="s">
-        <x:v>344</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="F50" s="2" t="s">
-        <x:v>344</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="G50" s="2" t="s">
         <x:v>29</x:v>
@@ -5963,7 +5980,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R50" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="S50" s="2"/>
       <x:c r="T50" s="2" t="s">
@@ -5980,7 +5997,7 @@
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
       <x:c r="A51" s="2" t="s">
-        <x:v>346</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B51" s="2" t="s">
         <x:v>24</x:v>
@@ -5989,13 +6006,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D51" s="2" t="s">
-        <x:v>275</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E51" s="2" t="s">
-        <x:v>347</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="F51" s="2" t="s">
-        <x:v>347</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="G51" s="2" t="s">
         <x:v>29</x:v>
@@ -6004,16 +6021,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I51" s="4" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J51" s="2" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="K51" s="4" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="J51" s="2" t="s">
-        <x:v>349</x:v>
-      </x:c>
-      <x:c r="K51" s="4" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="L51" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M51" s="2" t="s">
         <x:v>57</x:v>
@@ -6028,16 +6045,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q51" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R51" s="4" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="S51" s="2" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="T51" s="2" t="s">
         <x:v>351</x:v>
-      </x:c>
-      <x:c r="S51" s="2" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="T51" s="2" t="s">
-        <x:v>353</x:v>
       </x:c>
       <x:c r="U51" s="2" t="s">
         <x:v>65</x:v>
@@ -6050,7 +6067,7 @@
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
       <x:c r="A52" s="2" t="s">
-        <x:v>354</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
         <x:v>24</x:v>
@@ -6059,13 +6076,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D52" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E52" s="2" t="s">
-        <x:v>355</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F52" s="2" t="s">
-        <x:v>356</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="G52" s="2" t="s">
         <x:v>29</x:v>
@@ -6089,7 +6106,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R52" s="4" t="s">
-        <x:v>357</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="S52" s="2"/>
       <x:c r="T52" s="2"/>
@@ -6104,7 +6121,7 @@
     </x:row>
     <x:row r="53" ht="42" customHeight="1">
       <x:c r="A53" s="2" t="s">
-        <x:v>358</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
         <x:v>24</x:v>
@@ -6116,10 +6133,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="E53" s="2" t="s">
-        <x:v>359</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="F53" s="2" t="s">
-        <x:v>360</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="G53" s="2" t="s">
         <x:v>29</x:v>
@@ -6143,10 +6160,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R53" s="4" t="s">
-        <x:v>361</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="S53" s="2" t="s">
-        <x:v>362</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="T53" s="2"/>
       <x:c r="U53" s="2" t="s">
@@ -6160,7 +6177,7 @@
     </x:row>
     <x:row r="54" ht="42" customHeight="1">
       <x:c r="A54" s="2" t="s">
-        <x:v>363</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
         <x:v>24</x:v>
@@ -6172,10 +6189,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E54" s="2" t="s">
-        <x:v>364</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F54" s="2" t="s">
-        <x:v>338</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="G54" s="2" t="s">
         <x:v>29</x:v>
@@ -6199,10 +6216,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R54" s="4" t="s">
-        <x:v>365</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="S54" s="2" t="s">
-        <x:v>366</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="T54" s="2"/>
       <x:c r="U54" s="2" t="s">
@@ -6216,7 +6233,7 @@
     </x:row>
     <x:row r="55" ht="42" customHeight="1">
       <x:c r="A55" s="2" t="s">
-        <x:v>367</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B55" s="2" t="s">
         <x:v>24</x:v>
@@ -6228,10 +6245,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E55" s="2" t="s">
-        <x:v>368</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="F55" s="2" t="s">
-        <x:v>369</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="G55" s="2" t="s">
         <x:v>29</x:v>
@@ -6240,33 +6257,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I55" s="4" t="s">
-        <x:v>370</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="J55" s="2" t="s">
-        <x:v>371</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K55" s="4"/>
       <x:c r="L55" s="2"/>
       <x:c r="M55" s="2"/>
       <x:c r="N55" s="2"/>
       <x:c r="O55" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P55" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q55" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R55" s="4" t="s">
-        <x:v>372</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="S55" s="2" t="s">
-        <x:v>373</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="T55" s="2"/>
       <x:c r="U55" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V55" s="2"/>
       <x:c r="W55" s="2"/>
@@ -6276,7 +6293,7 @@
     </x:row>
     <x:row r="56" ht="42" customHeight="1">
       <x:c r="A56" s="2" t="s">
-        <x:v>374</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B56" s="2" t="s">
         <x:v>24</x:v>
@@ -6288,10 +6305,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E56" s="2" t="s">
-        <x:v>375</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F56" s="2" t="s">
-        <x:v>376</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G56" s="2" t="s">
         <x:v>29</x:v>
@@ -6300,33 +6317,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I56" s="4" t="s">
-        <x:v>377</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="J56" s="2" t="s">
-        <x:v>375</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="K56" s="4"/>
       <x:c r="L56" s="2"/>
       <x:c r="M56" s="2"/>
       <x:c r="N56" s="2"/>
       <x:c r="O56" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P56" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q56" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="R56" s="4" t="s">
-        <x:v>378</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="S56" s="2" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="T56" s="2"/>
       <x:c r="U56" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V56" s="2"/>
       <x:c r="W56" s="2"/>
@@ -6336,7 +6353,7 @@
     </x:row>
     <x:row r="57" ht="42" customHeight="1">
       <x:c r="A57" s="2" t="s">
-        <x:v>380</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B57" s="2" t="s">
         <x:v>24</x:v>
@@ -6348,10 +6365,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E57" s="2" t="s">
-        <x:v>381</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F57" s="2" t="s">
-        <x:v>381</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="G57" s="2" t="s">
         <x:v>29</x:v>
@@ -6375,7 +6392,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R57" s="4" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="S57" s="2"/>
       <x:c r="T57" s="2"/>
@@ -6390,22 +6407,22 @@
     </x:row>
     <x:row r="58" ht="42" customHeight="1">
       <x:c r="A58" s="2" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B58" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C58" s="2" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D58" s="2" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="E58" s="2" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="D58" s="2" t="s">
+      <x:c r="F58" s="2" t="s">
         <x:v>385</x:v>
-      </x:c>
-      <x:c r="E58" s="2" t="s">
-        <x:v>386</x:v>
-      </x:c>
-      <x:c r="F58" s="2" t="s">
-        <x:v>387</x:v>
       </x:c>
       <x:c r="G58" s="2" t="s">
         <x:v>29</x:v>
@@ -6429,10 +6446,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R58" s="4" t="s">
-        <x:v>388</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="S58" s="2" t="s">
-        <x:v>389</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="T58" s="2"/>
       <x:c r="U58" s="2" t="s">
@@ -6446,22 +6463,22 @@
     </x:row>
     <x:row r="59" ht="42" customHeight="1">
       <x:c r="A59" s="2" t="s">
-        <x:v>390</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B59" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C59" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D59" s="2" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="E59" s="2" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="F59" s="2" t="s">
         <x:v>391</x:v>
-      </x:c>
-      <x:c r="E59" s="2" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F59" s="2" t="s">
-        <x:v>393</x:v>
       </x:c>
       <x:c r="G59" s="2" t="s">
         <x:v>29</x:v>
@@ -6470,25 +6487,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I59" s="4" t="s">
-        <x:v>394</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="J59" s="2" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K59" s="4" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="L59" s="2" t="s">
-        <x:v>302</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="M59" s="2" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="N59" s="2" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="O59" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="P59" s="2" t="s">
         <x:v>60</x:v>
@@ -6497,10 +6514,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R59" s="4" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="S59" s="2" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="T59" s="2"/>
       <x:c r="U59" s="2" t="s">
@@ -6514,22 +6531,22 @@
     </x:row>
     <x:row r="60" ht="42" customHeight="1">
       <x:c r="A60" s="2" t="s">
-        <x:v>398</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B60" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C60" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D60" s="2" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="E60" s="2" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="F60" s="2" t="s">
         <x:v>399</x:v>
-      </x:c>
-      <x:c r="E60" s="2" t="s">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="F60" s="2" t="s">
-        <x:v>401</x:v>
       </x:c>
       <x:c r="G60" s="2" t="s">
         <x:v>29</x:v>
@@ -6538,13 +6555,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I60" s="4" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="J60" s="2" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="K60" s="4" t="s">
         <x:v>402</x:v>
-      </x:c>
-      <x:c r="J60" s="2" t="s">
-        <x:v>403</x:v>
-      </x:c>
-      <x:c r="K60" s="4" t="s">
-        <x:v>404</x:v>
       </x:c>
       <x:c r="L60" s="2" t="s">
         <x:v>56</x:v>
@@ -6562,16 +6579,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q60" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R60" s="4" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="S60" s="2" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="T60" s="2" t="s">
         <x:v>405</x:v>
-      </x:c>
-      <x:c r="S60" s="2" t="s">
-        <x:v>406</x:v>
-      </x:c>
-      <x:c r="T60" s="2" t="s">
-        <x:v>407</x:v>
       </x:c>
       <x:c r="U60" s="2" t="s">
         <x:v>65</x:v>
@@ -6584,22 +6601,22 @@
     </x:row>
     <x:row r="61" ht="42" customHeight="1">
       <x:c r="A61" s="2" t="s">
-        <x:v>408</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B61" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C61" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D61" s="2" t="s">
-        <x:v>385</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E61" s="2" t="s">
-        <x:v>409</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="F61" s="2" t="s">
-        <x:v>410</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="G61" s="2" t="s">
         <x:v>29</x:v>
@@ -6608,16 +6625,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I61" s="4" t="s">
-        <x:v>411</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="J61" s="2" t="s">
-        <x:v>412</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="K61" s="4" t="s">
-        <x:v>411</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="L61" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="M61" s="2" t="s">
         <x:v>57</x:v>
@@ -6632,13 +6649,13 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q61" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R61" s="4" t="s">
-        <x:v>413</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="S61" s="2" t="s">
-        <x:v>414</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="T61" s="2"/>
       <x:c r="U61" s="2" t="s">
@@ -6652,22 +6669,22 @@
     </x:row>
     <x:row r="62" ht="42" customHeight="1">
       <x:c r="A62" s="2" t="s">
-        <x:v>415</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B62" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C62" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D62" s="2" t="s">
-        <x:v>391</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E62" s="2" t="s">
-        <x:v>416</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F62" s="2" t="s">
-        <x:v>416</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="G62" s="2" t="s">
         <x:v>29</x:v>
@@ -6676,16 +6693,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I62" s="4" t="s">
-        <x:v>417</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="J62" s="2" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="K62" s="4" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="K62" s="4" t="s">
-        <x:v>418</x:v>
-      </x:c>
       <x:c r="L62" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M62" s="2" t="s">
         <x:v>57</x:v>
@@ -6703,13 +6720,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R62" s="4" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="S62" s="2" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="T62" s="2" t="s">
         <x:v>419</x:v>
-      </x:c>
-      <x:c r="S62" s="2" t="s">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="T62" s="2" t="s">
-        <x:v>421</x:v>
       </x:c>
       <x:c r="U62" s="2" t="s">
         <x:v>65</x:v>
@@ -6722,22 +6739,22 @@
     </x:row>
     <x:row r="63" ht="42" customHeight="1">
       <x:c r="A63" s="2" t="s">
-        <x:v>422</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B63" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C63" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D63" s="2" t="s">
-        <x:v>385</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E63" s="2" t="s">
-        <x:v>423</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F63" s="2" t="s">
-        <x:v>423</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="G63" s="2" t="s">
         <x:v>29</x:v>
@@ -6746,13 +6763,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I63" s="4" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="J63" s="2" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="K63" s="4" t="s">
         <x:v>424</x:v>
-      </x:c>
-      <x:c r="J63" s="2" t="s">
-        <x:v>425</x:v>
-      </x:c>
-      <x:c r="K63" s="4" t="s">
-        <x:v>426</x:v>
       </x:c>
       <x:c r="L63" s="2" t="s">
         <x:v>56</x:v>
@@ -6773,13 +6790,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R63" s="4" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="S63" s="2" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="T63" s="2" t="s">
         <x:v>427</x:v>
-      </x:c>
-      <x:c r="S63" s="2" t="s">
-        <x:v>428</x:v>
-      </x:c>
-      <x:c r="T63" s="2" t="s">
-        <x:v>429</x:v>
       </x:c>
       <x:c r="U63" s="2" t="s">
         <x:v>65</x:v>
@@ -6792,22 +6809,22 @@
     </x:row>
     <x:row r="64" ht="42" customHeight="1">
       <x:c r="A64" s="2" t="s">
-        <x:v>430</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B64" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C64" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D64" s="2" t="s">
-        <x:v>391</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E64" s="2" t="s">
-        <x:v>431</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F64" s="2" t="s">
-        <x:v>431</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="G64" s="2" t="s">
         <x:v>29</x:v>
@@ -6816,13 +6833,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I64" s="4" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="J64" s="2" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="K64" s="4" t="s">
         <x:v>432</x:v>
-      </x:c>
-      <x:c r="J64" s="2" t="s">
-        <x:v>433</x:v>
-      </x:c>
-      <x:c r="K64" s="4" t="s">
-        <x:v>434</x:v>
       </x:c>
       <x:c r="L64" s="2" t="s">
         <x:v>56</x:v>
@@ -6843,10 +6860,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R64" s="4" t="s">
-        <x:v>435</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="S64" s="2" t="s">
-        <x:v>436</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="T64" s="2" t="s">
         <x:v>64</x:v>
@@ -6862,22 +6879,22 @@
     </x:row>
     <x:row r="65" ht="42" customHeight="1">
       <x:c r="A65" s="2" t="s">
-        <x:v>437</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B65" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C65" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D65" s="2" t="s">
-        <x:v>399</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="E65" s="2" t="s">
-        <x:v>438</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F65" s="2" t="s">
-        <x:v>400</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="G65" s="2" t="s">
         <x:v>29</x:v>
@@ -6886,35 +6903,35 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I65" s="4" t="s">
-        <x:v>439</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="J65" s="2" t="s">
-        <x:v>440</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="K65" s="4"/>
       <x:c r="L65" s="2"/>
       <x:c r="M65" s="2"/>
       <x:c r="N65" s="2"/>
       <x:c r="O65" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P65" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q65" s="2" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="R65" s="4" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="S65" s="2" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="R65" s="4" t="s">
+      <x:c r="T65" s="2" t="s">
         <x:v>442</x:v>
       </x:c>
-      <x:c r="S65" s="2" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="T65" s="2" t="s">
-        <x:v>444</x:v>
-      </x:c>
       <x:c r="U65" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V65" s="2"/>
       <x:c r="W65" s="2"/>
@@ -6924,22 +6941,22 @@
     </x:row>
     <x:row r="66" ht="42" customHeight="1">
       <x:c r="A66" s="2" t="s">
-        <x:v>445</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B66" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C66" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D66" s="2" t="s">
-        <x:v>391</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E66" s="2" t="s">
-        <x:v>446</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="F66" s="2" t="s">
-        <x:v>446</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="G66" s="2" t="s">
         <x:v>29</x:v>
@@ -6963,7 +6980,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R66" s="4" t="s">
-        <x:v>447</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="S66" s="2"/>
       <x:c r="T66" s="2"/>
@@ -6978,22 +6995,22 @@
     </x:row>
     <x:row r="67" ht="42" customHeight="1">
       <x:c r="A67" s="2" t="s">
-        <x:v>448</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B67" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C67" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D67" s="2" t="s">
-        <x:v>385</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E67" s="2" t="s">
-        <x:v>449</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="F67" s="2" t="s">
-        <x:v>449</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="G67" s="2" t="s">
         <x:v>29</x:v>
@@ -7002,16 +7019,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I67" s="4" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="J67" s="2" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="K67" s="4" t="s">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="J67" s="2" t="s">
-        <x:v>451</x:v>
-      </x:c>
-      <x:c r="K67" s="4" t="s">
-        <x:v>452</x:v>
-      </x:c>
       <x:c r="L67" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="M67" s="2" t="s">
         <x:v>57</x:v>
@@ -7029,10 +7046,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R67" s="4" t="s">
-        <x:v>453</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="S67" s="2" t="s">
-        <x:v>454</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="T67" s="2"/>
       <x:c r="U67" s="2" t="s">
@@ -7046,22 +7063,22 @@
     </x:row>
     <x:row r="68" ht="42" customHeight="1">
       <x:c r="A68" s="2" t="s">
-        <x:v>455</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B68" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C68" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D68" s="2" t="s">
-        <x:v>456</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E68" s="2" t="s">
-        <x:v>457</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F68" s="2" t="s">
-        <x:v>457</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="G68" s="2" t="s">
         <x:v>29</x:v>
@@ -7085,7 +7102,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R68" s="4" t="s">
-        <x:v>458</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="S68" s="2"/>
       <x:c r="T68" s="2"/>
@@ -7100,22 +7117,22 @@
     </x:row>
     <x:row r="69" ht="42" customHeight="1">
       <x:c r="A69" s="2" t="s">
-        <x:v>459</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B69" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C69" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D69" s="2" t="s">
-        <x:v>456</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E69" s="2" t="s">
-        <x:v>460</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F69" s="2" t="s">
-        <x:v>461</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="G69" s="2" t="s">
         <x:v>29</x:v>
@@ -7124,33 +7141,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I69" s="4" t="s">
-        <x:v>462</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="J69" s="2" t="s">
-        <x:v>460</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="K69" s="4"/>
       <x:c r="L69" s="2"/>
       <x:c r="M69" s="2"/>
       <x:c r="N69" s="2"/>
       <x:c r="O69" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P69" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q69" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="R69" s="4" t="s">
-        <x:v>463</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="S69" s="2" t="s">
-        <x:v>464</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="T69" s="2"/>
       <x:c r="U69" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V69" s="2"/>
       <x:c r="W69" s="2"/>
@@ -7160,22 +7177,22 @@
     </x:row>
     <x:row r="70" ht="42" customHeight="1">
       <x:c r="A70" s="2" t="s">
-        <x:v>465</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B70" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C70" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D70" s="2" t="s">
-        <x:v>456</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E70" s="2" t="s">
-        <x:v>466</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F70" s="2" t="s">
-        <x:v>466</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="G70" s="2" t="s">
         <x:v>29</x:v>
@@ -7184,13 +7201,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I70" s="4" t="s">
-        <x:v>467</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="J70" s="2" t="s">
-        <x:v>468</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="K70" s="4" t="s">
-        <x:v>467</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="L70" s="2" t="s">
         <x:v>56</x:v>
@@ -7208,13 +7225,13 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q70" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R70" s="4" t="s">
-        <x:v>469</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="S70" s="2" t="s">
-        <x:v>470</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="T70" s="2"/>
       <x:c r="U70" s="2" t="s">
@@ -7228,22 +7245,22 @@
     </x:row>
     <x:row r="71" ht="42" customHeight="1">
       <x:c r="A71" s="2" t="s">
-        <x:v>471</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B71" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C71" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D71" s="2" t="s">
-        <x:v>391</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E71" s="2" t="s">
-        <x:v>472</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F71" s="2" t="s">
-        <x:v>473</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G71" s="2" t="s">
         <x:v>29</x:v>
@@ -7252,33 +7269,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I71" s="4" t="s">
-        <x:v>474</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="J71" s="2" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="K71" s="4"/>
       <x:c r="L71" s="2"/>
       <x:c r="M71" s="2"/>
       <x:c r="N71" s="2"/>
       <x:c r="O71" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P71" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q71" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="R71" s="4" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="S71" s="2" t="s">
-        <x:v>477</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="T71" s="2"/>
       <x:c r="U71" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V71" s="2"/>
       <x:c r="W71" s="2"/>
@@ -7288,22 +7305,22 @@
     </x:row>
     <x:row r="72" ht="42" customHeight="1">
       <x:c r="A72" s="2" t="s">
-        <x:v>478</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B72" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C72" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D72" s="2" t="s">
-        <x:v>385</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E72" s="2" t="s">
-        <x:v>479</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="F72" s="2" t="s">
-        <x:v>480</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="G72" s="2" t="s">
         <x:v>29</x:v>
@@ -7327,7 +7344,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R72" s="4" t="s">
-        <x:v>481</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="S72" s="2"/>
       <x:c r="T72" s="2"/>
@@ -7342,22 +7359,22 @@
     </x:row>
     <x:row r="73" ht="42" customHeight="1">
       <x:c r="A73" s="2" t="s">
-        <x:v>482</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B73" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C73" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D73" s="2" t="s">
-        <x:v>391</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E73" s="2" t="s">
-        <x:v>483</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F73" s="2" t="s">
-        <x:v>483</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="G73" s="2" t="s">
         <x:v>29</x:v>
@@ -7366,33 +7383,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I73" s="4" t="s">
-        <x:v>484</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="J73" s="2" t="s">
-        <x:v>485</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="K73" s="4"/>
       <x:c r="L73" s="2"/>
       <x:c r="M73" s="2"/>
       <x:c r="N73" s="2"/>
       <x:c r="O73" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P73" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q73" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="R73" s="4" t="s">
-        <x:v>486</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="S73" s="2" t="s">
-        <x:v>487</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="T73" s="2"/>
       <x:c r="U73" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V73" s="2"/>
       <x:c r="W73" s="2"/>
@@ -7402,22 +7419,22 @@
     </x:row>
     <x:row r="74" ht="42" customHeight="1">
       <x:c r="A74" s="2" t="s">
-        <x:v>488</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B74" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C74" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D74" s="2" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="E74" s="2" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="F74" s="2" t="s">
         <x:v>489</x:v>
-      </x:c>
-      <x:c r="E74" s="2" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="F74" s="2" t="s">
-        <x:v>491</x:v>
       </x:c>
       <x:c r="G74" s="2" t="s">
         <x:v>29</x:v>
@@ -7426,37 +7443,37 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I74" s="4" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="J74" s="2" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="K74" s="4" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="J74" s="2" t="s">
-        <x:v>493</x:v>
-      </x:c>
-      <x:c r="K74" s="4" t="s">
-        <x:v>494</x:v>
-      </x:c>
       <x:c r="L74" s="2" t="s">
-        <x:v>302</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="M74" s="2" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="N74" s="2" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="O74" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="P74" s="2" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q74" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R74" s="4" t="s">
-        <x:v>495</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="S74" s="2" t="s">
-        <x:v>496</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="T74" s="2"/>
       <x:c r="U74" s="2" t="s">
@@ -7470,22 +7487,22 @@
     </x:row>
     <x:row r="75" ht="42" customHeight="1">
       <x:c r="A75" s="2" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B75" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C75" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D75" s="2" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="E75" s="2" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="F75" s="2" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="G75" s="2" t="s">
         <x:v>29</x:v>
@@ -7494,35 +7511,35 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I75" s="4" t="s">
-        <x:v>499</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="J75" s="2" t="s">
-        <x:v>500</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="K75" s="4"/>
       <x:c r="L75" s="2"/>
       <x:c r="M75" s="2"/>
       <x:c r="N75" s="2"/>
       <x:c r="O75" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P75" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q75" s="2" t="s">
-        <x:v>441</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="R75" s="4" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="S75" s="2" t="s">
-        <x:v>502</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="T75" s="2" t="s">
-        <x:v>444</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="U75" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V75" s="2"/>
       <x:c r="W75" s="2"/>
@@ -7532,22 +7549,22 @@
     </x:row>
     <x:row r="76" ht="42" customHeight="1">
       <x:c r="A76" s="2" t="s">
-        <x:v>503</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B76" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C76" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D76" s="2" t="s">
-        <x:v>385</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E76" s="2" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="F76" s="2" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="G76" s="2" t="s">
         <x:v>29</x:v>
@@ -7556,33 +7573,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I76" s="4" t="s">
-        <x:v>505</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="J76" s="2" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="K76" s="4"/>
       <x:c r="L76" s="2"/>
       <x:c r="M76" s="2"/>
       <x:c r="N76" s="2"/>
       <x:c r="O76" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P76" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q76" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R76" s="4" t="s">
-        <x:v>506</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="S76" s="2" t="s">
-        <x:v>507</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="T76" s="2"/>
       <x:c r="U76" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V76" s="2"/>
       <x:c r="W76" s="2"/>
@@ -7592,22 +7609,22 @@
     </x:row>
     <x:row r="77" ht="42" customHeight="1">
       <x:c r="A77" s="2" t="s">
-        <x:v>508</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B77" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C77" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D77" s="2" t="s">
-        <x:v>385</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E77" s="2" t="s">
-        <x:v>509</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="F77" s="2" t="s">
-        <x:v>510</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="G77" s="2" t="s">
         <x:v>29</x:v>
@@ -7631,7 +7648,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R77" s="4" t="s">
-        <x:v>511</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="S77" s="2"/>
       <x:c r="T77" s="2"/>
@@ -7646,22 +7663,22 @@
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
       <x:c r="A78" s="2" t="s">
-        <x:v>512</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B78" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C78" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D78" s="2" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="E78" s="2" t="s">
-        <x:v>513</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="F78" s="2" t="s">
-        <x:v>513</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="G78" s="2" t="s">
         <x:v>29</x:v>
@@ -7685,7 +7702,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R78" s="4" t="s">
-        <x:v>514</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="S78" s="2"/>
       <x:c r="T78" s="2"/>
@@ -7700,22 +7717,22 @@
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
       <x:c r="A79" s="2" t="s">
-        <x:v>515</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B79" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C79" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D79" s="2" t="s">
-        <x:v>385</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E79" s="2" t="s">
-        <x:v>516</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="F79" s="2" t="s">
-        <x:v>516</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="G79" s="2" t="s">
         <x:v>29</x:v>
@@ -7739,7 +7756,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R79" s="4" t="s">
-        <x:v>517</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="S79" s="2"/>
       <x:c r="T79" s="2" t="s">
@@ -7756,22 +7773,22 @@
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="2" t="s">
-        <x:v>518</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B80" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C80" s="2" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="D80" s="2" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="E80" s="2" t="s">
         <x:v>519</x:v>
       </x:c>
-      <x:c r="D80" s="2" t="s">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="E80" s="2" t="s">
-        <x:v>521</x:v>
-      </x:c>
       <x:c r="F80" s="2" t="s">
-        <x:v>521</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="G80" s="2" t="s">
         <x:v>29</x:v>
@@ -7795,7 +7812,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R80" s="4" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="S80" s="2"/>
       <x:c r="T80" s="2"/>
@@ -7810,22 +7827,22 @@
     </x:row>
     <x:row r="81" ht="42" customHeight="1">
       <x:c r="A81" s="2" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B81" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C81" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D81" s="2" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="E81" s="2" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="F81" s="2" t="s">
         <x:v>524</x:v>
-      </x:c>
-      <x:c r="E81" s="2" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="F81" s="2" t="s">
-        <x:v>526</x:v>
       </x:c>
       <x:c r="G81" s="2" t="s">
         <x:v>29</x:v>
@@ -7834,16 +7851,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I81" s="4" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="J81" s="2" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="K81" s="4" t="s">
         <x:v>527</x:v>
       </x:c>
-      <x:c r="J81" s="2" t="s">
-        <x:v>528</x:v>
-      </x:c>
-      <x:c r="K81" s="4" t="s">
-        <x:v>529</x:v>
-      </x:c>
       <x:c r="L81" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M81" s="2" t="s">
         <x:v>57</x:v>
@@ -7858,16 +7875,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q81" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R81" s="4" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="S81" s="2" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="T81" s="2" t="s">
         <x:v>530</x:v>
-      </x:c>
-      <x:c r="S81" s="2" t="s">
-        <x:v>531</x:v>
-      </x:c>
-      <x:c r="T81" s="2" t="s">
-        <x:v>532</x:v>
       </x:c>
       <x:c r="U81" s="2" t="s">
         <x:v>65</x:v>
@@ -7880,22 +7897,22 @@
     </x:row>
     <x:row r="82" ht="42" customHeight="1">
       <x:c r="A82" s="2" t="s">
-        <x:v>533</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B82" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C82" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D82" s="2" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E82" s="2" t="s">
-        <x:v>534</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="F82" s="2" t="s">
-        <x:v>534</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="G82" s="2" t="s">
         <x:v>29</x:v>
@@ -7904,25 +7921,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I82" s="4" t="s">
-        <x:v>535</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="J82" s="2" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="K82" s="4" t="s">
         <x:v>534</x:v>
       </x:c>
-      <x:c r="K82" s="4" t="s">
-        <x:v>536</x:v>
-      </x:c>
       <x:c r="L82" s="2" t="s">
-        <x:v>302</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="M82" s="2" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="N82" s="2" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="O82" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="P82" s="2" t="s">
         <x:v>60</x:v>
@@ -7931,10 +7948,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R82" s="4" t="s">
-        <x:v>537</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="S82" s="2" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="T82" s="2"/>
       <x:c r="U82" s="2" t="s">
@@ -7948,22 +7965,22 @@
     </x:row>
     <x:row r="83" ht="42" customHeight="1">
       <x:c r="A83" s="2" t="s">
-        <x:v>539</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B83" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C83" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D83" s="2" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="E83" s="2" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="F83" s="2" t="s">
         <x:v>540</x:v>
-      </x:c>
-      <x:c r="E83" s="2" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="F83" s="2" t="s">
-        <x:v>542</x:v>
       </x:c>
       <x:c r="G83" s="2" t="s">
         <x:v>29</x:v>
@@ -7987,10 +8004,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R83" s="4" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="S83" s="2" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="T83" s="2"/>
       <x:c r="U83" s="2" t="s">
@@ -8004,22 +8021,22 @@
     </x:row>
     <x:row r="84" ht="42" customHeight="1">
       <x:c r="A84" s="2" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B84" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C84" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D84" s="2" t="s">
-        <x:v>540</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="E84" s="2" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="F84" s="2" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="G84" s="2" t="s">
         <x:v>29</x:v>
@@ -8043,7 +8060,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R84" s="4" t="s">
-        <x:v>547</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="S84" s="2"/>
       <x:c r="T84" s="2"/>
@@ -8058,22 +8075,22 @@
     </x:row>
     <x:row r="85" ht="42" customHeight="1">
       <x:c r="A85" s="2" t="s">
-        <x:v>548</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B85" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C85" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D85" s="2" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E85" s="2" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="F85" s="2" t="s">
-        <x:v>549</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="G85" s="2" t="s">
         <x:v>29</x:v>
@@ -8082,13 +8099,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I85" s="4" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="J85" s="2" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="K85" s="4" t="s">
         <x:v>550</x:v>
-      </x:c>
-      <x:c r="J85" s="2" t="s">
-        <x:v>551</x:v>
-      </x:c>
-      <x:c r="K85" s="4" t="s">
-        <x:v>552</x:v>
       </x:c>
       <x:c r="L85" s="2" t="s">
         <x:v>56</x:v>
@@ -8106,13 +8123,13 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q85" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R85" s="4" t="s">
-        <x:v>553</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="S85" s="2" t="s">
-        <x:v>554</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="T85" s="2" t="s">
         <x:v>64</x:v>
@@ -8128,22 +8145,22 @@
     </x:row>
     <x:row r="86" ht="42" customHeight="1">
       <x:c r="A86" s="2" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B86" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C86" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D86" s="2" t="s">
-        <x:v>540</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="E86" s="2" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F86" s="2" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="G86" s="2" t="s">
         <x:v>29</x:v>
@@ -8167,7 +8184,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R86" s="4" t="s">
-        <x:v>557</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="S86" s="2"/>
       <x:c r="T86" s="2"/>
@@ -8182,22 +8199,22 @@
     </x:row>
     <x:row r="87" ht="42" customHeight="1">
       <x:c r="A87" s="2" t="s">
-        <x:v>558</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B87" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C87" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D87" s="2" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E87" s="2" t="s">
-        <x:v>559</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="F87" s="2" t="s">
-        <x:v>560</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="G87" s="2" t="s">
         <x:v>29</x:v>
@@ -8206,25 +8223,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I87" s="4" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="J87" s="2" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="K87" s="4" t="s">
         <x:v>561</x:v>
       </x:c>
-      <x:c r="J87" s="2" t="s">
-        <x:v>562</x:v>
-      </x:c>
-      <x:c r="K87" s="4" t="s">
-        <x:v>563</x:v>
-      </x:c>
       <x:c r="L87" s="2" t="s">
-        <x:v>302</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="M87" s="2" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="N87" s="2" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="O87" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="P87" s="2" t="s">
         <x:v>60</x:v>
@@ -8233,13 +8250,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R87" s="4" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="S87" s="2" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="T87" s="2" t="s">
         <x:v>564</x:v>
-      </x:c>
-      <x:c r="S87" s="2" t="s">
-        <x:v>565</x:v>
-      </x:c>
-      <x:c r="T87" s="2" t="s">
-        <x:v>566</x:v>
       </x:c>
       <x:c r="U87" s="2" t="s">
         <x:v>65</x:v>
@@ -8252,22 +8269,22 @@
     </x:row>
     <x:row r="88" ht="42" customHeight="1">
       <x:c r="A88" s="2" t="s">
-        <x:v>567</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B88" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C88" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D88" s="2" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E88" s="2" t="s">
-        <x:v>568</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F88" s="2" t="s">
-        <x:v>568</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="G88" s="2" t="s">
         <x:v>29</x:v>
@@ -8291,7 +8308,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R88" s="4" t="s">
-        <x:v>569</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="S88" s="2"/>
       <x:c r="T88" s="2"/>
@@ -8306,22 +8323,22 @@
     </x:row>
     <x:row r="89" ht="42" customHeight="1">
       <x:c r="A89" s="2" t="s">
-        <x:v>570</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B89" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C89" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D89" s="2" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E89" s="2" t="s">
-        <x:v>571</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F89" s="2" t="s">
-        <x:v>572</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G89" s="2" t="s">
         <x:v>29</x:v>
@@ -8345,7 +8362,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R89" s="4" t="s">
-        <x:v>573</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="S89" s="2"/>
       <x:c r="T89" s="2"/>
@@ -8360,22 +8377,22 @@
     </x:row>
     <x:row r="90" ht="42" customHeight="1">
       <x:c r="A90" s="2" t="s">
-        <x:v>574</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B90" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C90" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D90" s="2" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E90" s="2" t="s">
-        <x:v>575</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="F90" s="2" t="s">
-        <x:v>575</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="G90" s="2" t="s">
         <x:v>29</x:v>
@@ -8384,25 +8401,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I90" s="4" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="J90" s="2" t="s">
-        <x:v>577</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="K90" s="4" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="L90" s="2" t="s">
-        <x:v>302</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="M90" s="2" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="N90" s="2" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="O90" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="P90" s="2" t="s">
         <x:v>60</x:v>
@@ -8411,10 +8428,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R90" s="4" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="S90" s="2" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="T90" s="2"/>
       <x:c r="U90" s="2" t="s">
@@ -8428,22 +8445,22 @@
     </x:row>
     <x:row r="91" ht="42" customHeight="1">
       <x:c r="A91" s="2" t="s">
-        <x:v>580</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B91" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C91" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D91" s="2" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="E91" s="2" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="F91" s="2" t="s">
         <x:v>581</x:v>
-      </x:c>
-      <x:c r="E91" s="2" t="s">
-        <x:v>582</x:v>
-      </x:c>
-      <x:c r="F91" s="2" t="s">
-        <x:v>583</x:v>
       </x:c>
       <x:c r="G91" s="2" t="s">
         <x:v>29</x:v>
@@ -8452,13 +8469,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I91" s="4" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="J91" s="2" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="K91" s="4" t="s">
         <x:v>584</x:v>
-      </x:c>
-      <x:c r="J91" s="2" t="s">
-        <x:v>585</x:v>
-      </x:c>
-      <x:c r="K91" s="4" t="s">
-        <x:v>586</x:v>
       </x:c>
       <x:c r="L91" s="2" t="s">
         <x:v>56</x:v>
@@ -8476,16 +8493,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q91" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R91" s="4" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="S91" s="2" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="T91" s="2" t="s">
         <x:v>587</x:v>
-      </x:c>
-      <x:c r="S91" s="2" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="T91" s="2" t="s">
-        <x:v>589</x:v>
       </x:c>
       <x:c r="U91" s="2" t="s">
         <x:v>65</x:v>
@@ -8498,22 +8515,22 @@
     </x:row>
     <x:row r="92" ht="42" customHeight="1">
       <x:c r="A92" s="2" t="s">
-        <x:v>590</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B92" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C92" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D92" s="2" t="s">
-        <x:v>581</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="E92" s="2" t="s">
-        <x:v>591</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="F92" s="2" t="s">
-        <x:v>592</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="G92" s="2" t="s">
         <x:v>29</x:v>
@@ -8522,33 +8539,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I92" s="4" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="J92" s="2" t="s">
-        <x:v>594</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="K92" s="4"/>
       <x:c r="L92" s="2"/>
       <x:c r="M92" s="2"/>
       <x:c r="N92" s="2"/>
       <x:c r="O92" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P92" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q92" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R92" s="4" t="s">
-        <x:v>595</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="S92" s="2" t="s">
-        <x:v>596</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="T92" s="2"/>
       <x:c r="U92" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V92" s="2"/>
       <x:c r="W92" s="2"/>
@@ -8558,22 +8575,22 @@
     </x:row>
     <x:row r="93" ht="42" customHeight="1">
       <x:c r="A93" s="2" t="s">
-        <x:v>597</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B93" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D93" s="2" t="s">
-        <x:v>540</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="E93" s="2" t="s">
-        <x:v>598</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="F93" s="2" t="s">
-        <x:v>599</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="G93" s="2" t="s">
         <x:v>29</x:v>
@@ -8597,10 +8614,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R93" s="4" t="s">
-        <x:v>600</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="S93" s="2" t="s">
-        <x:v>601</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="T93" s="2"/>
       <x:c r="U93" s="2" t="s">
@@ -8614,22 +8631,22 @@
     </x:row>
     <x:row r="94" ht="42" customHeight="1">
       <x:c r="A94" s="2" t="s">
-        <x:v>602</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B94" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D94" s="2" t="s">
-        <x:v>540</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="E94" s="2" t="s">
-        <x:v>603</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="F94" s="2" t="s">
-        <x:v>541</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="G94" s="2" t="s">
         <x:v>29</x:v>
@@ -8638,35 +8655,35 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I94" s="4" t="s">
-        <x:v>604</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="J94" s="2" t="s">
-        <x:v>605</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="K94" s="4"/>
       <x:c r="L94" s="2"/>
       <x:c r="M94" s="2"/>
       <x:c r="N94" s="2"/>
       <x:c r="O94" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P94" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q94" s="2" t="s">
-        <x:v>441</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="R94" s="4" t="s">
-        <x:v>606</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="S94" s="2" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="T94" s="2" t="s">
-        <x:v>444</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="U94" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V94" s="2"/>
       <x:c r="W94" s="2"/>
@@ -8676,22 +8693,22 @@
     </x:row>
     <x:row r="95" ht="42" customHeight="1">
       <x:c r="A95" s="2" t="s">
-        <x:v>608</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B95" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C95" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D95" s="2" t="s">
-        <x:v>540</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="E95" s="2" t="s">
-        <x:v>609</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="F95" s="2" t="s">
-        <x:v>609</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="G95" s="2" t="s">
         <x:v>29</x:v>
@@ -8715,7 +8732,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R95" s="4" t="s">
-        <x:v>610</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="S95" s="2"/>
       <x:c r="T95" s="2" t="s">
@@ -8732,22 +8749,22 @@
     </x:row>
     <x:row r="96" ht="42" customHeight="1">
       <x:c r="A96" s="2" t="s">
-        <x:v>611</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B96" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C96" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D96" s="2" t="s">
-        <x:v>581</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="E96" s="2" t="s">
-        <x:v>592</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="F96" s="2" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="G96" s="2" t="s">
         <x:v>29</x:v>
@@ -8771,10 +8788,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R96" s="4" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="S96" s="2" t="s">
-        <x:v>614</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="T96" s="2"/>
       <x:c r="U96" s="2" t="s">
@@ -8788,22 +8805,22 @@
     </x:row>
     <x:row r="97" ht="42" customHeight="1">
       <x:c r="A97" s="2" t="s">
-        <x:v>615</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B97" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C97" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D97" s="2" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="E97" s="2" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="F97" s="2" t="s">
         <x:v>581</x:v>
-      </x:c>
-      <x:c r="E97" s="2" t="s">
-        <x:v>616</x:v>
-      </x:c>
-      <x:c r="F97" s="2" t="s">
-        <x:v>583</x:v>
       </x:c>
       <x:c r="G97" s="2" t="s">
         <x:v>29</x:v>
@@ -8812,16 +8829,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I97" s="4" t="s">
-        <x:v>617</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="J97" s="2" t="s">
-        <x:v>583</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="K97" s="4" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="L97" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M97" s="2" t="s">
         <x:v>57</x:v>
@@ -8836,16 +8853,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q97" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R97" s="4" t="s">
-        <x:v>619</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="S97" s="2" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="T97" s="2" t="s">
-        <x:v>532</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="U97" s="2" t="s">
         <x:v>65</x:v>
@@ -8858,22 +8875,22 @@
     </x:row>
     <x:row r="98" ht="42" customHeight="1">
       <x:c r="A98" s="2" t="s">
-        <x:v>621</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="B98" s="2" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C98" s="2" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="D98" s="2" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="E98" s="2" t="s">
         <x:v>622</x:v>
       </x:c>
-      <x:c r="D98" s="2" t="s">
-        <x:v>623</x:v>
-      </x:c>
-      <x:c r="E98" s="2" t="s">
-        <x:v>624</x:v>
-      </x:c>
       <x:c r="F98" s="2" t="s">
-        <x:v>624</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="G98" s="2" t="s">
         <x:v>29</x:v>
@@ -8897,7 +8914,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R98" s="4" t="s">
-        <x:v>625</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="S98" s="2"/>
       <x:c r="T98" s="2"/>
@@ -8912,22 +8929,22 @@
     </x:row>
     <x:row r="99" ht="42" customHeight="1">
       <x:c r="A99" s="2" t="s">
-        <x:v>626</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="B99" s="2" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C99" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="D99" s="2" t="s">
-        <x:v>623</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="E99" s="2" t="s">
-        <x:v>627</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="F99" s="2" t="s">
-        <x:v>627</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="G99" s="2" t="s">
         <x:v>29</x:v>
@@ -8951,7 +8968,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R99" s="4" t="s">
-        <x:v>628</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="S99" s="2"/>
       <x:c r="T99" s="2"/>
@@ -8966,22 +8983,22 @@
     </x:row>
     <x:row r="100" ht="42" customHeight="1">
       <x:c r="A100" s="2" t="s">
-        <x:v>629</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="B100" s="2" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C100" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="D100" s="2" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="E100" s="2" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="F100" s="2" t="s">
         <x:v>630</x:v>
-      </x:c>
-      <x:c r="E100" s="2" t="s">
-        <x:v>631</x:v>
-      </x:c>
-      <x:c r="F100" s="2" t="s">
-        <x:v>632</x:v>
       </x:c>
       <x:c r="G100" s="2" t="s">
         <x:v>29</x:v>
@@ -8990,33 +9007,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I100" s="4" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="J100" s="2" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="K100" s="4"/>
       <x:c r="L100" s="2"/>
       <x:c r="M100" s="2"/>
       <x:c r="N100" s="2"/>
       <x:c r="O100" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P100" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q100" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R100" s="4" t="s">
-        <x:v>635</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="S100" s="2" t="s">
-        <x:v>636</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="T100" s="2"/>
       <x:c r="U100" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V100" s="2"/>
       <x:c r="W100" s="2"/>
@@ -9026,22 +9043,22 @@
     </x:row>
     <x:row r="101" ht="42" customHeight="1">
       <x:c r="A101" s="2" t="s">
-        <x:v>637</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="B101" s="2" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C101" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="D101" s="2" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="E101" s="2" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="F101" s="2" t="s">
         <x:v>638</x:v>
-      </x:c>
-      <x:c r="E101" s="2" t="s">
-        <x:v>639</x:v>
-      </x:c>
-      <x:c r="F101" s="2" t="s">
-        <x:v>640</x:v>
       </x:c>
       <x:c r="G101" s="2" t="s">
         <x:v>29</x:v>
@@ -9065,10 +9082,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R101" s="4" t="s">
-        <x:v>641</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="S101" s="2" t="s">
-        <x:v>642</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="T101" s="2"/>
       <x:c r="U101" s="2" t="s">
@@ -9082,22 +9099,22 @@
     </x:row>
     <x:row r="102" ht="42" customHeight="1">
       <x:c r="A102" s="2" t="s">
-        <x:v>643</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C102" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="D102" s="2" t="s">
-        <x:v>623</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="E102" s="2" t="s">
-        <x:v>644</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="F102" s="2" t="s">
-        <x:v>644</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="G102" s="2" t="s">
         <x:v>29</x:v>
@@ -9106,25 +9123,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I102" s="4" t="s">
-        <x:v>645</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="J102" s="2" t="s">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="K102" s="4" t="s">
         <x:v>644</x:v>
       </x:c>
-      <x:c r="K102" s="4" t="s">
-        <x:v>646</x:v>
-      </x:c>
       <x:c r="L102" s="2" t="s">
-        <x:v>302</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="M102" s="2" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="N102" s="2" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="O102" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="P102" s="2" t="s">
         <x:v>60</x:v>
@@ -9133,10 +9150,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R102" s="4" t="s">
-        <x:v>647</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="S102" s="2" t="s">
-        <x:v>648</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="T102" s="2"/>
       <x:c r="U102" s="2" t="s">
@@ -9150,22 +9167,22 @@
     </x:row>
     <x:row r="103" ht="42" customHeight="1">
       <x:c r="A103" s="2" t="s">
-        <x:v>649</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C103" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="D103" s="2" t="s">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="E103" s="2" t="s">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="F103" s="2" t="s">
         <x:v>650</x:v>
-      </x:c>
-      <x:c r="E103" s="2" t="s">
-        <x:v>651</x:v>
-      </x:c>
-      <x:c r="F103" s="2" t="s">
-        <x:v>652</x:v>
       </x:c>
       <x:c r="G103" s="2" t="s">
         <x:v>29</x:v>
@@ -9174,16 +9191,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I103" s="4" t="s">
-        <x:v>653</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="J103" s="2" t="s">
-        <x:v>654</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="K103" s="4" t="s">
-        <x:v>653</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="L103" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M103" s="2" t="s">
         <x:v>57</x:v>
@@ -9198,13 +9215,13 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q103" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R103" s="4" t="s">
-        <x:v>655</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="S103" s="2" t="s">
-        <x:v>656</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="T103" s="2"/>
       <x:c r="U103" s="2" t="s">
@@ -9218,22 +9235,22 @@
     </x:row>
     <x:row r="104" ht="42" customHeight="1">
       <x:c r="A104" s="2" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="C104" s="2" t="s">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="D104" s="2" t="s">
+        <x:v>657</x:v>
+      </x:c>
+      <x:c r="E104" s="2" t="s">
         <x:v>658</x:v>
       </x:c>
-      <x:c r="D104" s="2" t="s">
+      <x:c r="F104" s="2" t="s">
         <x:v>659</x:v>
-      </x:c>
-      <x:c r="E104" s="2" t="s">
-        <x:v>660</x:v>
-      </x:c>
-      <x:c r="F104" s="2" t="s">
-        <x:v>661</x:v>
       </x:c>
       <x:c r="G104" s="2" t="s">
         <x:v>29</x:v>
@@ -9242,43 +9259,43 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I104" s="4" t="s">
-        <x:v>662</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="J104" s="2" t="s">
-        <x:v>660</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="K104" s="4" t="s">
-        <x:v>663</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="L104" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M104" s="2" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="N104" s="2" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="O104" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="P104" s="2" t="s">
-        <x:v>664</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="Q104" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="R104" s="4" t="s">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="S104" s="2" t="s">
+        <x:v>660</x:v>
+      </x:c>
+      <x:c r="T104" s="2" t="s">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="U104" s="2" t="s">
         <x:v>665</x:v>
-      </x:c>
-      <x:c r="S104" s="2" t="s">
-        <x:v>662</x:v>
-      </x:c>
-      <x:c r="T104" s="2" t="s">
-        <x:v>666</x:v>
-      </x:c>
-      <x:c r="U104" s="2" t="s">
-        <x:v>667</x:v>
       </x:c>
       <x:c r="V104" s="2"/>
       <x:c r="W104" s="2"/>
@@ -9288,22 +9305,22 @@
     </x:row>
     <x:row r="105" ht="42" customHeight="1">
       <x:c r="A105" s="2" t="s">
-        <x:v>668</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="C105" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D105" s="2" t="s">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="E105" s="2" t="s">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="F105" s="2" t="s">
         <x:v>669</x:v>
-      </x:c>
-      <x:c r="E105" s="2" t="s">
-        <x:v>670</x:v>
-      </x:c>
-      <x:c r="F105" s="2" t="s">
-        <x:v>671</x:v>
       </x:c>
       <x:c r="G105" s="2" t="s">
         <x:v>29</x:v>
@@ -9312,16 +9329,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I105" s="4" t="s">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="J105" s="2" t="s">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="K105" s="4" t="s">
         <x:v>672</x:v>
       </x:c>
-      <x:c r="J105" s="2" t="s">
-        <x:v>673</x:v>
-      </x:c>
-      <x:c r="K105" s="4" t="s">
-        <x:v>674</x:v>
-      </x:c>
       <x:c r="L105" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M105" s="2" t="s">
         <x:v>57</x:v>
@@ -9336,16 +9353,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q105" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R105" s="4" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="S105" s="2" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="T105" s="2" t="s">
         <x:v>675</x:v>
-      </x:c>
-      <x:c r="S105" s="2" t="s">
-        <x:v>676</x:v>
-      </x:c>
-      <x:c r="T105" s="2" t="s">
-        <x:v>677</x:v>
       </x:c>
       <x:c r="U105" s="2" t="s">
         <x:v>65</x:v>
@@ -9358,22 +9375,22 @@
     </x:row>
     <x:row r="106" ht="42" customHeight="1">
       <x:c r="A106" s="2" t="s">
-        <x:v>678</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="C106" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D106" s="2" t="s">
-        <x:v>659</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="E106" s="2" t="s">
-        <x:v>679</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="F106" s="2" t="s">
-        <x:v>680</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="G106" s="2" t="s">
         <x:v>29</x:v>
@@ -9397,7 +9414,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R106" s="4" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="S106" s="2"/>
       <x:c r="T106" s="2"/>
@@ -9412,22 +9429,22 @@
     </x:row>
     <x:row r="107" ht="42" customHeight="1">
       <x:c r="A107" s="2" t="s">
-        <x:v>682</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="C107" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D107" s="2" t="s">
-        <x:v>659</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="E107" s="2" t="s">
-        <x:v>683</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="F107" s="2" t="s">
-        <x:v>683</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="G107" s="2" t="s">
         <x:v>29</x:v>
@@ -9436,33 +9453,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I107" s="4" t="s">
-        <x:v>684</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="J107" s="2" t="s">
-        <x:v>683</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="K107" s="4"/>
       <x:c r="L107" s="2"/>
       <x:c r="M107" s="2"/>
       <x:c r="N107" s="2"/>
       <x:c r="O107" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P107" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q107" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R107" s="4" t="s">
-        <x:v>685</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="S107" s="2" t="s">
-        <x:v>686</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="T107" s="2"/>
       <x:c r="U107" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V107" s="2"/>
       <x:c r="W107" s="2"/>
@@ -9472,22 +9489,22 @@
     </x:row>
     <x:row r="108" ht="42" customHeight="1">
       <x:c r="A108" s="2" t="s">
-        <x:v>687</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="B108" s="2" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="C108" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D108" s="2" t="s">
-        <x:v>659</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="E108" s="2" t="s">
-        <x:v>688</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="F108" s="2" t="s">
-        <x:v>688</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="G108" s="2" t="s">
         <x:v>29</x:v>
@@ -9511,7 +9528,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R108" s="4" t="s">
-        <x:v>689</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="S108" s="2"/>
       <x:c r="T108" s="2" t="s">
@@ -9528,22 +9545,22 @@
     </x:row>
     <x:row r="109" ht="42" customHeight="1">
       <x:c r="A109" s="2" t="s">
-        <x:v>690</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="C109" s="2" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="D109" s="2" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="E109" s="2" t="s">
         <x:v>691</x:v>
       </x:c>
-      <x:c r="D109" s="2" t="s">
-        <x:v>692</x:v>
-      </x:c>
-      <x:c r="E109" s="2" t="s">
-        <x:v>693</x:v>
-      </x:c>
       <x:c r="F109" s="2" t="s">
-        <x:v>693</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G109" s="2" t="s">
         <x:v>29</x:v>
@@ -9552,33 +9569,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I109" s="4" t="s">
-        <x:v>694</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="J109" s="2" t="s">
-        <x:v>695</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="K109" s="4"/>
       <x:c r="L109" s="2"/>
       <x:c r="M109" s="2"/>
       <x:c r="N109" s="2"/>
       <x:c r="O109" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P109" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="Q109" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R109" s="4" t="s">
-        <x:v>696</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="S109" s="2" t="s">
-        <x:v>697</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="T109" s="2"/>
       <x:c r="U109" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V109" s="2"/>
       <x:c r="W109" s="2"/>
@@ -9588,22 +9605,22 @@
     </x:row>
     <x:row r="110" ht="42" customHeight="1">
       <x:c r="A110" s="2" t="s">
-        <x:v>698</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="C110" s="2" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="D110" s="2" t="s">
-        <x:v>692</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="E110" s="2" t="s">
-        <x:v>699</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="F110" s="2" t="s">
-        <x:v>699</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="G110" s="2" t="s">
         <x:v>29</x:v>
@@ -9627,7 +9644,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R110" s="4" t="s">
-        <x:v>700</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="S110" s="2"/>
       <x:c r="T110" s="2" t="s">
@@ -9644,22 +9661,22 @@
     </x:row>
     <x:row r="111" ht="42" customHeight="1">
       <x:c r="A111" s="2" t="s">
-        <x:v>701</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="C111" s="2" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="D111" s="2" t="s">
-        <x:v>702</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="E111" s="2" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="F111" s="2" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G111" s="2" t="s">
         <x:v>29</x:v>
@@ -9683,7 +9700,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R111" s="4" t="s">
-        <x:v>704</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="S111" s="2"/>
       <x:c r="T111" s="2"/>
@@ -9698,22 +9715,22 @@
     </x:row>
     <x:row r="112" ht="42" customHeight="1">
       <x:c r="A112" s="2" t="s">
-        <x:v>705</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="B112" s="2" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="C112" s="2" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="D112" s="2" t="s">
-        <x:v>692</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="E112" s="2" t="s">
-        <x:v>706</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="F112" s="2" t="s">
-        <x:v>707</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="G112" s="2" t="s">
         <x:v>29</x:v>
@@ -9737,7 +9754,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R112" s="4" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="S112" s="2"/>
       <x:c r="T112" s="2"/>
@@ -9752,22 +9769,22 @@
     </x:row>
     <x:row r="113" ht="42" customHeight="1">
       <x:c r="A113" s="2" t="s">
-        <x:v>709</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="C113" s="2" t="s">
+        <x:v>708</x:v>
+      </x:c>
+      <x:c r="D113" s="2" t="s">
+        <x:v>709</x:v>
+      </x:c>
+      <x:c r="E113" s="2" t="s">
         <x:v>710</x:v>
       </x:c>
-      <x:c r="D113" s="2" t="s">
+      <x:c r="F113" s="2" t="s">
         <x:v>711</x:v>
-      </x:c>
-      <x:c r="E113" s="2" t="s">
-        <x:v>712</x:v>
-      </x:c>
-      <x:c r="F113" s="2" t="s">
-        <x:v>713</x:v>
       </x:c>
       <x:c r="G113" s="2" t="s">
         <x:v>29</x:v>
@@ -9791,7 +9808,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R113" s="4" t="s">
-        <x:v>714</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="S113" s="2"/>
       <x:c r="T113" s="2"/>
@@ -9806,22 +9823,22 @@
     </x:row>
     <x:row r="114" ht="42" customHeight="1">
       <x:c r="A114" s="2" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="C114" s="2" t="s">
-        <x:v>710</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="D114" s="2" t="s">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="E114" s="2" t="s">
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="F114" s="2" t="s">
         <x:v>716</x:v>
-      </x:c>
-      <x:c r="E114" s="2" t="s">
-        <x:v>717</x:v>
-      </x:c>
-      <x:c r="F114" s="2" t="s">
-        <x:v>718</x:v>
       </x:c>
       <x:c r="G114" s="2" t="s">
         <x:v>29</x:v>
@@ -9830,13 +9847,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I114" s="4" t="s">
+        <x:v>717</x:v>
+      </x:c>
+      <x:c r="J114" s="2" t="s">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c r="K114" s="4" t="s">
         <x:v>719</x:v>
-      </x:c>
-      <x:c r="J114" s="2" t="s">
-        <x:v>720</x:v>
-      </x:c>
-      <x:c r="K114" s="4" t="s">
-        <x:v>721</x:v>
       </x:c>
       <x:c r="L114" s="2" t="s">
         <x:v>56</x:v>
@@ -9857,13 +9874,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="R114" s="4" t="s">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="S114" s="2" t="s">
+        <x:v>721</x:v>
+      </x:c>
+      <x:c r="T114" s="2" t="s">
         <x:v>722</x:v>
-      </x:c>
-      <x:c r="S114" s="2" t="s">
-        <x:v>723</x:v>
-      </x:c>
-      <x:c r="T114" s="2" t="s">
-        <x:v>724</x:v>
       </x:c>
       <x:c r="U114" s="2" t="s">
         <x:v>65</x:v>
@@ -9876,22 +9893,22 @@
     </x:row>
     <x:row r="115" ht="42" customHeight="1">
       <x:c r="A115" s="2" t="s">
-        <x:v>725</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="C115" s="2" t="s">
+        <x:v>724</x:v>
+      </x:c>
+      <x:c r="D115" s="2" t="s">
+        <x:v>725</x:v>
+      </x:c>
+      <x:c r="E115" s="2" t="s">
         <x:v>726</x:v>
       </x:c>
-      <x:c r="D115" s="2" t="s">
-        <x:v>727</x:v>
-      </x:c>
-      <x:c r="E115" s="2" t="s">
-        <x:v>728</x:v>
-      </x:c>
       <x:c r="F115" s="2" t="s">
-        <x:v>728</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="G115" s="2" t="s">
         <x:v>29</x:v>
@@ -9900,13 +9917,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="I115" s="4" t="s">
-        <x:v>729</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="J115" s="2" t="s">
+        <x:v>726</x:v>
+      </x:c>
+      <x:c r="K115" s="4" t="s">
         <x:v>728</x:v>
-      </x:c>
-      <x:c r="K115" s="4" t="s">
-        <x:v>730</x:v>
       </x:c>
       <x:c r="L115" s="2" t="s">
         <x:v>56</x:v>
@@ -9924,16 +9941,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Q115" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R115" s="4" t="s">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c r="S115" s="2" t="s">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="T115" s="2" t="s">
         <x:v>731</x:v>
-      </x:c>
-      <x:c r="S115" s="2" t="s">
-        <x:v>732</x:v>
-      </x:c>
-      <x:c r="T115" s="2" t="s">
-        <x:v>733</x:v>
       </x:c>
       <x:c r="U115" s="2" t="s">
         <x:v>65</x:v>
@@ -9946,22 +9963,22 @@
     </x:row>
     <x:row r="116" ht="42" customHeight="1">
       <x:c r="A116" s="2" t="s">
-        <x:v>734</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="B116" s="2" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="C116" s="2" t="s">
-        <x:v>726</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="D116" s="2" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E116" s="2" t="s">
-        <x:v>735</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="F116" s="2" t="s">
-        <x:v>736</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="G116" s="2" t="s">
         <x:v>29</x:v>
@@ -9985,7 +10002,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R116" s="4" t="s">
-        <x:v>737</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="S116" s="2"/>
       <x:c r="T116" s="2"/>
@@ -10000,22 +10017,22 @@
     </x:row>
     <x:row r="117" ht="42" customHeight="1">
       <x:c r="A117" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B117" s="3" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C117" s="3" t="s">
+        <x:v>737</x:v>
+      </x:c>
+      <x:c r="D117" s="3" t="s">
+        <x:v>738</x:v>
+      </x:c>
+      <x:c r="E117" s="3" t="s">
         <x:v>739</x:v>
       </x:c>
-      <x:c r="D117" s="3" t="s">
-        <x:v>740</x:v>
-      </x:c>
-      <x:c r="E117" s="3" t="s">
-        <x:v>741</x:v>
-      </x:c>
       <x:c r="F117" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="G117" s="3" t="s">
         <x:v>29</x:v>
@@ -10039,7 +10056,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="R117" s="5" t="s">
-        <x:v>742</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="S117" s="3"/>
       <x:c r="T117" s="3"/>
@@ -10072,55 +10089,55 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R5c5cb511f9174bb5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R816b2b1b49af4372"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="R2fbc8c34401d4696"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R70515154b72c484d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="Rd6961ada84a24cab"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="Ra8bfc8fad18d4af2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="R7029fdb0c7034d46"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="R2d84657936884abe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="Rbdbdf2f19b1a4919"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="R54177e6efed64abe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="R75b3b73fd9d242b4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R4d94383b46524367"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R3bc2b2c67d1341c6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R121519b2079144bc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R2bb716764146401f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="R725e7f3d53ed4142"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="Rffe98eb621774859"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="R533fe849af00449a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="R2f58a6e5452444c6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R9f69ee3ac01f43b9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="Rb028a6fbd72d4d28"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="Rcc8098f036ec40d3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Rfd0e05f16e10407d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="Rb5f1cff263eb4ef7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="R4b18753b1a2c4e90"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="Rd9e45dbc3e7749df"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Re0f8e023cd2e4417"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="Rb6a438b94f724e6c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R5a20f01e46b640f5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R0a0ec7c60d6c4436"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="Ra192084f6e484ba9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="R0ee6307f9a3d44f5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R43209ec63c0b4154"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R4db21bde1e3a400b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="Rfd9dc3c6512b43ec"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R7910902f71ae4563"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="R4a12cff2ac7c4cc7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R5a2d0f96c539415f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Rc1cb169b2ed7465f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="Rb5fb01bbe7474d41"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="R2619a68161764b3b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="Re09fd8bd35db4710"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="Rb055ebba446948fc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="Rfd4901d499ba46e5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R5ee1bd6c8a2c4ee9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R33ffe6539f694917"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R36c21bb35cea42c3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="Rc66d91c0c35d4d9a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R030f50c53ea541b1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="R21d4bf280c194bb6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R40a7c891a40b45d1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="R1dec603ce7bc4442"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="R58eab9b80d2e48aa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="Re1b3f238751249e7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="Ra970982095f946f7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="Rf3517abf58164de7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="Rd24b1909ccb74f07"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R601ec40c61494945"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R22b1120e94af448b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R711f65b57d3c481c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="R664067dfb2fc4734"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="Rc6a5c2a1787d4d0d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="Ra997f5e3528a4f61"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="Rea5e0ab37ef94eca"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="Ra92777122ace4fa8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="Rdaf850a540994fa3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="Rc85eed91b6144c20"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Ra23d89b8997946dc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="Rc1060bd494074cbf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rf7ab0c0783b94e6a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="R48107b64042b4726"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Rc37d29bef5314698"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="Rf69c924e779d4d52"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R2540eba63ed74ea6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R34b7bc34ef9845ea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="Rca14e5f1547c4f03"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="R5933b7a1c7754cb0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R9dfc103acc5b42b2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Ree6b52da1e0e4ead"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="R5ab94717331449b9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R6dea6cb3368049eb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="R0e453b2d8a6446d2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R125cbeaceead4c41"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Rea06ff48f8474e22"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="Rd185949d182e491b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="Rbad2cdb4f39f4942"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R4fc587f1b8c44278"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="R23dc279fa1dd46d8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="R8f2a81d061df49ae"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R36ff7854aadb465e"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R755524f7b0964f8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R149744666abf47a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10141,25 +10158,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>741</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>742</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
         <x:v>743</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="E1" s="1" t="s">
         <x:v>744</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="F1" s="1" t="s">
         <x:v>745</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>746</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>747</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>748</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>749</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="16.5">
@@ -10190,7 +10207,7 @@
     </x:row>
     <x:row r="3" ht="16.5">
       <x:c r="A3" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B3" s="2">
         <x:v>22</x:v>
@@ -10216,7 +10233,7 @@
     </x:row>
     <x:row r="4" ht="16.5">
       <x:c r="A4" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B4" s="2">
         <x:v>18</x:v>
@@ -10242,7 +10259,7 @@
     </x:row>
     <x:row r="5" ht="16.5">
       <x:c r="A5" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B5" s="2">
         <x:v>6</x:v>
@@ -10268,7 +10285,7 @@
     </x:row>
     <x:row r="6" ht="16.5">
       <x:c r="A6" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B6" s="2">
         <x:v>5</x:v>
@@ -10294,7 +10311,7 @@
     </x:row>
     <x:row r="7" ht="16.5">
       <x:c r="A7" s="2" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B7" s="2">
         <x:v>4</x:v>
@@ -10320,7 +10337,7 @@
     </x:row>
     <x:row r="8" ht="16.5">
       <x:c r="A8" s="2" t="s">
-        <x:v>710</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B8" s="2">
         <x:v>2</x:v>
@@ -10346,7 +10363,7 @@
     </x:row>
     <x:row r="9" ht="16.5">
       <x:c r="A9" s="2" t="s">
-        <x:v>726</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="B9" s="2">
         <x:v>2</x:v>
@@ -10372,7 +10389,7 @@
     </x:row>
     <x:row r="10" ht="16.5">
       <x:c r="A10" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="B10" s="3">
         <x:v>1</x:v>
@@ -10399,7 +10416,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e420795aea544db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra227091762b6444d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10660,7 +10677,7 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>750</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
         <x:v>59</x:v>
@@ -10679,7 +10696,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
       <x:c r="D12" s="2"/>
@@ -10700,13 +10717,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>751</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
         <x:v>59</x:v>
@@ -10725,13 +10742,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C14" s="2" t="s">
-        <x:v>125</x:v>
-      </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>752</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="E14" s="2" t="s">
         <x:v>59</x:v>
@@ -10754,13 +10771,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>753</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="E15" s="2" t="s">
         <x:v>59</x:v>
@@ -10779,13 +10796,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="C16" s="2" t="s">
+      <x:c r="D16" s="2" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="D16" s="2" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
         <x:v>59</x:v>
@@ -10804,20 +10821,20 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D17" s="2"/>
       <x:c r="E17" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H17" s="2"/>
       <x:c r="I17" s="2"/>
@@ -10827,7 +10844,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>155</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C18" s="2"/>
       <x:c r="D18" s="2"/>
@@ -10848,19 +10865,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C19" s="2" t="s">
-        <x:v>161</x:v>
-      </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>162</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
         <x:v>65</x:v>
@@ -10873,7 +10890,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C20" s="2"/>
       <x:c r="D20" s="2"/>
@@ -10894,7 +10911,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C21" s="2"/>
       <x:c r="D21" s="2"/>
@@ -10915,7 +10932,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C22" s="2"/>
       <x:c r="D22" s="2"/>
@@ -10936,19 +10953,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C23" s="2" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="D23" s="2" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
         <x:v>65</x:v>
@@ -10961,7 +10978,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
-        <x:v>191</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C24" s="2"/>
       <x:c r="D24" s="2"/>
@@ -10982,7 +10999,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C25" s="2"/>
       <x:c r="D25" s="2"/>
@@ -11003,7 +11020,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>203</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C26" s="2"/>
       <x:c r="D26" s="2"/>
@@ -11024,7 +11041,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C27" s="2"/>
       <x:c r="D27" s="2"/>
@@ -11045,7 +11062,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>212</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C28" s="2"/>
       <x:c r="D28" s="2"/>
@@ -11066,7 +11083,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C29" s="2"/>
       <x:c r="D29" s="2"/>
@@ -11087,7 +11104,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C30" s="2"/>
       <x:c r="D30" s="2"/>
@@ -11108,20 +11125,20 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C31" s="2" t="s">
-        <x:v>228</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D31" s="2"/>
       <x:c r="E31" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F31" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G31" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H31" s="2"/>
       <x:c r="I31" s="2"/>
@@ -11131,7 +11148,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C32" s="2"/>
       <x:c r="D32" s="2"/>
@@ -11152,7 +11169,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C33" s="2"/>
       <x:c r="D33" s="2"/>
@@ -11173,13 +11190,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B34" s="2" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C34" s="2" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="C34" s="2" t="s">
+      <x:c r="D34" s="2" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="D34" s="2" t="s">
-        <x:v>244</x:v>
       </x:c>
       <x:c r="E34" s="2" t="s">
         <x:v>59</x:v>
@@ -11198,13 +11215,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B35" s="2" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C35" s="2" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>754</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="E35" s="2" t="s">
         <x:v>59</x:v>
@@ -11223,13 +11240,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B36" s="2" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C36" s="2" t="s">
-        <x:v>257</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>755</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="E36" s="2" t="s">
         <x:v>59</x:v>
@@ -11248,7 +11265,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B37" s="2" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C37" s="2"/>
       <x:c r="D37" s="2"/>
@@ -11273,7 +11290,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>270</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C38" s="2"/>
       <x:c r="D38" s="2"/>
@@ -11294,20 +11311,20 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C39" s="2" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D39" s="2"/>
       <x:c r="E39" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F39" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G39" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H39" s="2"/>
       <x:c r="I39" s="2"/>
@@ -11317,19 +11334,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B40" s="2" t="s">
-        <x:v>281</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C40" s="2" t="s">
-        <x:v>282</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D40" s="2" t="s">
-        <x:v>756</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="E40" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F40" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G40" s="2" t="s">
         <x:v>65</x:v>
@@ -11342,13 +11359,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B41" s="2" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C41" s="2" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="C41" s="2" t="s">
-        <x:v>290</x:v>
-      </x:c>
       <x:c r="D41" s="2" t="s">
-        <x:v>291</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E41" s="2" t="s">
         <x:v>59</x:v>
@@ -11367,7 +11384,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B42" s="2" t="s">
-        <x:v>295</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C42" s="2"/>
       <x:c r="D42" s="2"/>
@@ -11388,19 +11405,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B43" s="2" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="C43" s="2" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="C43" s="2" t="s">
-        <x:v>300</x:v>
-      </x:c>
       <x:c r="D43" s="2" t="s">
-        <x:v>301</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E43" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F43" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G43" s="2" t="s">
         <x:v>65</x:v>
@@ -11413,19 +11430,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B44" s="2" t="s">
-        <x:v>309</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C44" s="2" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="D44" s="2" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="D44" s="2" t="s">
-        <x:v>312</x:v>
       </x:c>
       <x:c r="E44" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F44" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G44" s="2" t="s">
         <x:v>65</x:v>
@@ -11438,13 +11455,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B45" s="2" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="C45" s="2" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="C45" s="2" t="s">
+      <x:c r="D45" s="2" t="s">
         <x:v>319</x:v>
-      </x:c>
-      <x:c r="D45" s="2" t="s">
-        <x:v>321</x:v>
       </x:c>
       <x:c r="E45" s="2" t="s">
         <x:v>59</x:v>
@@ -11463,19 +11480,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B46" s="2" t="s">
-        <x:v>325</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C46" s="2" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="D46" s="2" t="s">
         <x:v>326</x:v>
-      </x:c>
-      <x:c r="D46" s="2" t="s">
-        <x:v>328</x:v>
       </x:c>
       <x:c r="E46" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F46" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G46" s="2" t="s">
         <x:v>65</x:v>
@@ -11488,7 +11505,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B47" s="2" t="s">
-        <x:v>333</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C47" s="2"/>
       <x:c r="D47" s="2"/>
@@ -11509,7 +11526,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B48" s="2" t="s">
-        <x:v>337</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C48" s="2"/>
       <x:c r="D48" s="2"/>
@@ -11530,7 +11547,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B49" s="2" t="s">
-        <x:v>341</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C49" s="2"/>
       <x:c r="D49" s="2"/>
@@ -11551,7 +11568,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B50" s="2" t="s">
-        <x:v>344</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C50" s="2"/>
       <x:c r="D50" s="2"/>
@@ -11572,19 +11589,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B51" s="2" t="s">
-        <x:v>347</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C51" s="2" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="D51" s="2" t="s">
         <x:v>348</x:v>
-      </x:c>
-      <x:c r="D51" s="2" t="s">
-        <x:v>350</x:v>
       </x:c>
       <x:c r="E51" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F51" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G51" s="2" t="s">
         <x:v>65</x:v>
@@ -11597,7 +11614,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>355</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C52" s="2"/>
       <x:c r="D52" s="2"/>
@@ -11618,7 +11635,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
-        <x:v>359</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C53" s="2"/>
       <x:c r="D53" s="2"/>
@@ -11639,7 +11656,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
-        <x:v>364</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C54" s="2"/>
       <x:c r="D54" s="2"/>
@@ -11660,20 +11677,20 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B55" s="2" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="C55" s="2" t="s">
         <x:v>368</x:v>
-      </x:c>
-      <x:c r="C55" s="2" t="s">
-        <x:v>370</x:v>
       </x:c>
       <x:c r="D55" s="2"/>
       <x:c r="E55" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F55" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G55" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H55" s="2"/>
       <x:c r="I55" s="2"/>
@@ -11683,20 +11700,20 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B56" s="2" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="C56" s="2" t="s">
         <x:v>375</x:v>
-      </x:c>
-      <x:c r="C56" s="2" t="s">
-        <x:v>377</x:v>
       </x:c>
       <x:c r="D56" s="2"/>
       <x:c r="E56" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F56" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="G56" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H56" s="2"/>
       <x:c r="I56" s="2"/>
@@ -11706,7 +11723,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B57" s="2" t="s">
-        <x:v>381</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C57" s="2"/>
       <x:c r="D57" s="2"/>
@@ -11724,10 +11741,10 @@
     </x:row>
     <x:row r="58" ht="16.5">
       <x:c r="A58" s="2" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B58" s="2" t="s">
         <x:v>384</x:v>
-      </x:c>
-      <x:c r="B58" s="2" t="s">
-        <x:v>386</x:v>
       </x:c>
       <x:c r="C58" s="2"/>
       <x:c r="D58" s="2"/>
@@ -11745,19 +11762,19 @@
     </x:row>
     <x:row r="59" ht="16.5">
       <x:c r="A59" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B59" s="2" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="C59" s="2" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="C59" s="2" t="s">
-        <x:v>394</x:v>
-      </x:c>
       <x:c r="D59" s="2" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="E59" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F59" s="2" t="s">
         <x:v>61</x:v>
@@ -11770,22 +11787,22 @@
     </x:row>
     <x:row r="60" ht="16.5">
       <x:c r="A60" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B60" s="2" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="C60" s="2" t="s">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="C60" s="2" t="s">
+      <x:c r="D60" s="2" t="s">
         <x:v>402</x:v>
-      </x:c>
-      <x:c r="D60" s="2" t="s">
-        <x:v>404</x:v>
       </x:c>
       <x:c r="E60" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F60" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G60" s="2" t="s">
         <x:v>65</x:v>
@@ -11795,22 +11812,22 @@
     </x:row>
     <x:row r="61" ht="16.5">
       <x:c r="A61" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B61" s="2" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="C61" s="2" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="C61" s="2" t="s">
-        <x:v>411</x:v>
-      </x:c>
       <x:c r="D61" s="2" t="s">
-        <x:v>411</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="E61" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F61" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G61" s="2" t="s">
         <x:v>65</x:v>
@@ -11820,16 +11837,16 @@
     </x:row>
     <x:row r="62" ht="16.5">
       <x:c r="A62" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B62" s="2" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="C62" s="2" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="D62" s="2" t="s">
         <x:v>416</x:v>
-      </x:c>
-      <x:c r="C62" s="2" t="s">
-        <x:v>417</x:v>
-      </x:c>
-      <x:c r="D62" s="2" t="s">
-        <x:v>418</x:v>
       </x:c>
       <x:c r="E62" s="2" t="s">
         <x:v>59</x:v>
@@ -11845,16 +11862,16 @@
     </x:row>
     <x:row r="63" ht="33">
       <x:c r="A63" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B63" s="2" t="s">
-        <x:v>423</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C63" s="2" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D63" s="2" t="s">
         <x:v>424</x:v>
-      </x:c>
-      <x:c r="D63" s="2" t="s">
-        <x:v>426</x:v>
       </x:c>
       <x:c r="E63" s="2" t="s">
         <x:v>59</x:v>
@@ -11870,16 +11887,16 @@
     </x:row>
     <x:row r="64" ht="16.5">
       <x:c r="A64" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B64" s="2" t="s">
-        <x:v>431</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="C64" s="2" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="D64" s="2" t="s">
         <x:v>432</x:v>
-      </x:c>
-      <x:c r="D64" s="2" t="s">
-        <x:v>434</x:v>
       </x:c>
       <x:c r="E64" s="2" t="s">
         <x:v>59</x:v>
@@ -11895,33 +11912,33 @@
     </x:row>
     <x:row r="65" ht="33">
       <x:c r="A65" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B65" s="2" t="s">
-        <x:v>438</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C65" s="2" t="s">
-        <x:v>439</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="D65" s="2"/>
       <x:c r="E65" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F65" s="2" t="s">
-        <x:v>441</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="G65" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H65" s="2"/>
       <x:c r="I65" s="2"/>
     </x:row>
     <x:row r="66" ht="16.5">
       <x:c r="A66" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B66" s="2" t="s">
-        <x:v>446</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C66" s="2"/>
       <x:c r="D66" s="2"/>
@@ -11939,16 +11956,16 @@
     </x:row>
     <x:row r="67" ht="33">
       <x:c r="A67" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B67" s="2" t="s">
-        <x:v>449</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C67" s="2" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="D67" s="2" t="s">
         <x:v>450</x:v>
-      </x:c>
-      <x:c r="D67" s="2" t="s">
-        <x:v>452</x:v>
       </x:c>
       <x:c r="E67" s="2" t="s">
         <x:v>59</x:v>
@@ -11964,10 +11981,10 @@
     </x:row>
     <x:row r="68" ht="16.5">
       <x:c r="A68" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B68" s="2" t="s">
-        <x:v>457</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="C68" s="2"/>
       <x:c r="D68" s="2"/>
@@ -11985,45 +12002,45 @@
     </x:row>
     <x:row r="69" ht="33">
       <x:c r="A69" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B69" s="2" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C69" s="2" t="s">
         <x:v>460</x:v>
-      </x:c>
-      <x:c r="C69" s="2" t="s">
-        <x:v>462</x:v>
       </x:c>
       <x:c r="D69" s="2"/>
       <x:c r="E69" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F69" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="G69" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H69" s="2"/>
       <x:c r="I69" s="2"/>
     </x:row>
     <x:row r="70" ht="16.5">
       <x:c r="A70" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B70" s="2" t="s">
-        <x:v>466</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="C70" s="2" t="s">
-        <x:v>467</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="D70" s="2" t="s">
-        <x:v>467</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="E70" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F70" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G70" s="2" t="s">
         <x:v>65</x:v>
@@ -12033,33 +12050,33 @@
     </x:row>
     <x:row r="71" ht="33">
       <x:c r="A71" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B71" s="2" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="C71" s="2" t="s">
         <x:v>472</x:v>
-      </x:c>
-      <x:c r="C71" s="2" t="s">
-        <x:v>474</x:v>
       </x:c>
       <x:c r="D71" s="2"/>
       <x:c r="E71" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F71" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="G71" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H71" s="2"/>
       <x:c r="I71" s="2"/>
     </x:row>
     <x:row r="72" ht="16.5">
       <x:c r="A72" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B72" s="2" t="s">
-        <x:v>479</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C72" s="2"/>
       <x:c r="D72" s="2"/>
@@ -12077,45 +12094,45 @@
     </x:row>
     <x:row r="73" ht="33">
       <x:c r="A73" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B73" s="2" t="s">
-        <x:v>483</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="C73" s="2" t="s">
-        <x:v>484</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="D73" s="2"/>
       <x:c r="E73" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F73" s="2" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="G73" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H73" s="2"/>
       <x:c r="I73" s="2"/>
     </x:row>
     <x:row r="74" ht="16.5">
       <x:c r="A74" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B74" s="2" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="C74" s="2" t="s">
         <x:v>490</x:v>
       </x:c>
-      <x:c r="C74" s="2" t="s">
+      <x:c r="D74" s="2" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="D74" s="2" t="s">
-        <x:v>494</x:v>
-      </x:c>
       <x:c r="E74" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F74" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G74" s="2" t="s">
         <x:v>65</x:v>
@@ -12125,56 +12142,56 @@
     </x:row>
     <x:row r="75" ht="33">
       <x:c r="A75" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B75" s="2" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="C75" s="2" t="s">
-        <x:v>499</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="D75" s="2"/>
       <x:c r="E75" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F75" s="2" t="s">
-        <x:v>441</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="G75" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H75" s="2"/>
       <x:c r="I75" s="2"/>
     </x:row>
     <x:row r="76" ht="33">
       <x:c r="A76" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B76" s="2" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="C76" s="2" t="s">
-        <x:v>505</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D76" s="2"/>
       <x:c r="E76" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F76" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G76" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H76" s="2"/>
       <x:c r="I76" s="2"/>
     </x:row>
     <x:row r="77" ht="16.5">
       <x:c r="A77" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B77" s="2" t="s">
-        <x:v>509</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="C77" s="2"/>
       <x:c r="D77" s="2"/>
@@ -12192,10 +12209,10 @@
     </x:row>
     <x:row r="78" ht="16.5">
       <x:c r="A78" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B78" s="2" t="s">
-        <x:v>513</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="C78" s="2"/>
       <x:c r="D78" s="2"/>
@@ -12213,10 +12230,10 @@
     </x:row>
     <x:row r="79" ht="16.5">
       <x:c r="A79" s="2" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B79" s="2" t="s">
-        <x:v>516</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="C79" s="2"/>
       <x:c r="D79" s="2"/>
@@ -12234,10 +12251,10 @@
     </x:row>
     <x:row r="80" ht="16.5">
       <x:c r="A80" s="2" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B80" s="2" t="s">
         <x:v>519</x:v>
-      </x:c>
-      <x:c r="B80" s="2" t="s">
-        <x:v>521</x:v>
       </x:c>
       <x:c r="C80" s="2"/>
       <x:c r="D80" s="2"/>
@@ -12255,22 +12272,22 @@
     </x:row>
     <x:row r="81" ht="33">
       <x:c r="A81" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B81" s="2" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="C81" s="2" t="s">
         <x:v>525</x:v>
       </x:c>
-      <x:c r="C81" s="2" t="s">
+      <x:c r="D81" s="2" t="s">
         <x:v>527</x:v>
-      </x:c>
-      <x:c r="D81" s="2" t="s">
-        <x:v>529</x:v>
       </x:c>
       <x:c r="E81" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F81" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G81" s="2" t="s">
         <x:v>65</x:v>
@@ -12280,19 +12297,19 @@
     </x:row>
     <x:row r="82" ht="16.5">
       <x:c r="A82" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B82" s="2" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="C82" s="2" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="D82" s="2" t="s">
         <x:v>534</x:v>
       </x:c>
-      <x:c r="C82" s="2" t="s">
-        <x:v>535</x:v>
-      </x:c>
-      <x:c r="D82" s="2" t="s">
-        <x:v>536</x:v>
-      </x:c>
       <x:c r="E82" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F82" s="2" t="s">
         <x:v>61</x:v>
@@ -12305,10 +12322,10 @@
     </x:row>
     <x:row r="83" ht="16.5">
       <x:c r="A83" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B83" s="2" t="s">
-        <x:v>541</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="C83" s="2"/>
       <x:c r="D83" s="2"/>
@@ -12326,10 +12343,10 @@
     </x:row>
     <x:row r="84" ht="16.5">
       <x:c r="A84" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B84" s="2" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C84" s="2"/>
       <x:c r="D84" s="2"/>
@@ -12347,22 +12364,22 @@
     </x:row>
     <x:row r="85" ht="16.5">
       <x:c r="A85" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B85" s="2" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C85" s="2" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="D85" s="2" t="s">
         <x:v>550</x:v>
-      </x:c>
-      <x:c r="D85" s="2" t="s">
-        <x:v>552</x:v>
       </x:c>
       <x:c r="E85" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F85" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G85" s="2" t="s">
         <x:v>65</x:v>
@@ -12372,10 +12389,10 @@
     </x:row>
     <x:row r="86" ht="16.5">
       <x:c r="A86" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B86" s="2" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C86" s="2"/>
       <x:c r="D86" s="2"/>
@@ -12393,19 +12410,19 @@
     </x:row>
     <x:row r="87" ht="16.5">
       <x:c r="A87" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B87" s="2" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="C87" s="2" t="s">
         <x:v>559</x:v>
       </x:c>
-      <x:c r="C87" s="2" t="s">
+      <x:c r="D87" s="2" t="s">
         <x:v>561</x:v>
       </x:c>
-      <x:c r="D87" s="2" t="s">
-        <x:v>563</x:v>
-      </x:c>
       <x:c r="E87" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F87" s="2" t="s">
         <x:v>61</x:v>
@@ -12418,10 +12435,10 @@
     </x:row>
     <x:row r="88" ht="16.5">
       <x:c r="A88" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B88" s="2" t="s">
-        <x:v>568</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C88" s="2"/>
       <x:c r="D88" s="2"/>
@@ -12439,10 +12456,10 @@
     </x:row>
     <x:row r="89" ht="16.5">
       <x:c r="A89" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B89" s="2" t="s">
-        <x:v>571</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="C89" s="2"/>
       <x:c r="D89" s="2"/>
@@ -12460,19 +12477,19 @@
     </x:row>
     <x:row r="90" ht="16.5">
       <x:c r="A90" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B90" s="2" t="s">
-        <x:v>575</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="C90" s="2" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="D90" s="2" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="E90" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F90" s="2" t="s">
         <x:v>61</x:v>
@@ -12485,22 +12502,22 @@
     </x:row>
     <x:row r="91" ht="16.5">
       <x:c r="A91" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B91" s="2" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="C91" s="2" t="s">
         <x:v>582</x:v>
       </x:c>
-      <x:c r="C91" s="2" t="s">
+      <x:c r="D91" s="2" t="s">
         <x:v>584</x:v>
-      </x:c>
-      <x:c r="D91" s="2" t="s">
-        <x:v>586</x:v>
       </x:c>
       <x:c r="E91" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F91" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G91" s="2" t="s">
         <x:v>65</x:v>
@@ -12510,33 +12527,33 @@
     </x:row>
     <x:row r="92" ht="33">
       <x:c r="A92" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B92" s="2" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="C92" s="2" t="s">
         <x:v>591</x:v>
-      </x:c>
-      <x:c r="C92" s="2" t="s">
-        <x:v>593</x:v>
       </x:c>
       <x:c r="D92" s="2"/>
       <x:c r="E92" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F92" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G92" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H92" s="2"/>
       <x:c r="I92" s="2"/>
     </x:row>
     <x:row r="93" ht="16.5">
       <x:c r="A93" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B93" s="2" t="s">
-        <x:v>598</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="C93" s="2"/>
       <x:c r="D93" s="2"/>
@@ -12554,33 +12571,33 @@
     </x:row>
     <x:row r="94" ht="33">
       <x:c r="A94" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B94" s="2" t="s">
-        <x:v>603</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>604</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D94" s="2"/>
       <x:c r="E94" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F94" s="2" t="s">
-        <x:v>441</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="G94" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H94" s="2"/>
       <x:c r="I94" s="2"/>
     </x:row>
     <x:row r="95" ht="16.5">
       <x:c r="A95" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B95" s="2" t="s">
-        <x:v>609</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="C95" s="2"/>
       <x:c r="D95" s="2"/>
@@ -12598,10 +12615,10 @@
     </x:row>
     <x:row r="96" ht="16.5">
       <x:c r="A96" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B96" s="2" t="s">
-        <x:v>592</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="C96" s="2"/>
       <x:c r="D96" s="2"/>
@@ -12619,22 +12636,22 @@
     </x:row>
     <x:row r="97" ht="16.5">
       <x:c r="A97" s="2" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B97" s="2" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="C97" s="2" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="D97" s="2" t="s">
         <x:v>616</x:v>
-      </x:c>
-      <x:c r="C97" s="2" t="s">
-        <x:v>617</x:v>
-      </x:c>
-      <x:c r="D97" s="2" t="s">
-        <x:v>618</x:v>
       </x:c>
       <x:c r="E97" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F97" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G97" s="2" t="s">
         <x:v>65</x:v>
@@ -12644,10 +12661,10 @@
     </x:row>
     <x:row r="98" ht="16.5">
       <x:c r="A98" s="2" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="B98" s="2" t="s">
         <x:v>622</x:v>
-      </x:c>
-      <x:c r="B98" s="2" t="s">
-        <x:v>624</x:v>
       </x:c>
       <x:c r="C98" s="2"/>
       <x:c r="D98" s="2"/>
@@ -12665,10 +12682,10 @@
     </x:row>
     <x:row r="99" ht="16.5">
       <x:c r="A99" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B99" s="2" t="s">
-        <x:v>627</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="C99" s="2"/>
       <x:c r="D99" s="2"/>
@@ -12686,33 +12703,33 @@
     </x:row>
     <x:row r="100" ht="33">
       <x:c r="A100" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B100" s="2" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="C100" s="2" t="s">
         <x:v>631</x:v>
-      </x:c>
-      <x:c r="C100" s="2" t="s">
-        <x:v>633</x:v>
       </x:c>
       <x:c r="D100" s="2"/>
       <x:c r="E100" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F100" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G100" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H100" s="2"/>
       <x:c r="I100" s="2"/>
     </x:row>
     <x:row r="101" ht="16.5">
       <x:c r="A101" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B101" s="2" t="s">
-        <x:v>639</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="C101" s="2"/>
       <x:c r="D101" s="2"/>
@@ -12730,19 +12747,19 @@
     </x:row>
     <x:row r="102" ht="16.5">
       <x:c r="A102" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="C102" s="2" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="D102" s="2" t="s">
         <x:v>644</x:v>
       </x:c>
-      <x:c r="C102" s="2" t="s">
-        <x:v>645</x:v>
-      </x:c>
-      <x:c r="D102" s="2" t="s">
-        <x:v>646</x:v>
-      </x:c>
       <x:c r="E102" s="2" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F102" s="2" t="s">
         <x:v>61</x:v>
@@ -12755,22 +12772,22 @@
     </x:row>
     <x:row r="103" ht="16.5">
       <x:c r="A103" s="2" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="C103" s="2" t="s">
         <x:v>651</x:v>
       </x:c>
-      <x:c r="C103" s="2" t="s">
-        <x:v>653</x:v>
-      </x:c>
       <x:c r="D103" s="2" t="s">
-        <x:v>653</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E103" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F103" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G103" s="2" t="s">
         <x:v>65</x:v>
@@ -12780,22 +12797,22 @@
     </x:row>
     <x:row r="104" ht="33">
       <x:c r="A104" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="C104" s="2" t="s">
         <x:v>670</x:v>
       </x:c>
-      <x:c r="C104" s="2" t="s">
+      <x:c r="D104" s="2" t="s">
         <x:v>672</x:v>
-      </x:c>
-      <x:c r="D104" s="2" t="s">
-        <x:v>674</x:v>
       </x:c>
       <x:c r="E104" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F104" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G104" s="2" t="s">
         <x:v>65</x:v>
@@ -12805,10 +12822,10 @@
     </x:row>
     <x:row r="105" ht="16.5">
       <x:c r="A105" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>679</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="C105" s="2"/>
       <x:c r="D105" s="2"/>
@@ -12826,33 +12843,33 @@
     </x:row>
     <x:row r="106" ht="33">
       <x:c r="A106" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>683</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="C106" s="2" t="s">
-        <x:v>684</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="D106" s="2"/>
       <x:c r="E106" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F106" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G106" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H106" s="2"/>
       <x:c r="I106" s="2"/>
     </x:row>
     <x:row r="107" ht="16.5">
       <x:c r="A107" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>688</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="C107" s="2"/>
       <x:c r="D107" s="2"/>
@@ -12870,33 +12887,33 @@
     </x:row>
     <x:row r="108" ht="33">
       <x:c r="A108" s="2" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="B108" s="2" t="s">
         <x:v>691</x:v>
       </x:c>
-      <x:c r="B108" s="2" t="s">
-        <x:v>693</x:v>
-      </x:c>
       <x:c r="C108" s="2" t="s">
-        <x:v>694</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="D108" s="2"/>
       <x:c r="E108" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F108" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G108" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H108" s="2"/>
       <x:c r="I108" s="2"/>
     </x:row>
     <x:row r="109" ht="16.5">
       <x:c r="A109" s="2" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B109" s="2" t="s">
-        <x:v>699</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C109" s="2"/>
       <x:c r="D109" s="2"/>
@@ -12914,10 +12931,10 @@
     </x:row>
     <x:row r="110" ht="16.5">
       <x:c r="A110" s="2" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B110" s="2" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="C110" s="2"/>
       <x:c r="D110" s="2"/>
@@ -12935,10 +12952,10 @@
     </x:row>
     <x:row r="111" ht="16.5">
       <x:c r="A111" s="2" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B111" s="2" t="s">
-        <x:v>706</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="C111" s="2"/>
       <x:c r="D111" s="2"/>
@@ -12956,10 +12973,10 @@
     </x:row>
     <x:row r="112" ht="16.5">
       <x:c r="A112" s="2" t="s">
+        <x:v>708</x:v>
+      </x:c>
+      <x:c r="B112" s="2" t="s">
         <x:v>710</x:v>
-      </x:c>
-      <x:c r="B112" s="2" t="s">
-        <x:v>712</x:v>
       </x:c>
       <x:c r="C112" s="2"/>
       <x:c r="D112" s="2"/>
@@ -12977,16 +12994,16 @@
     </x:row>
     <x:row r="113" ht="16.5">
       <x:c r="A113" s="2" t="s">
-        <x:v>710</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B113" s="2" t="s">
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="C113" s="2" t="s">
         <x:v>717</x:v>
       </x:c>
-      <x:c r="C113" s="2" t="s">
+      <x:c r="D113" s="2" t="s">
         <x:v>719</x:v>
-      </x:c>
-      <x:c r="D113" s="2" t="s">
-        <x:v>721</x:v>
       </x:c>
       <x:c r="E113" s="2" t="s">
         <x:v>59</x:v>
@@ -13002,22 +13019,22 @@
     </x:row>
     <x:row r="114" ht="33">
       <x:c r="A114" s="2" t="s">
+        <x:v>724</x:v>
+      </x:c>
+      <x:c r="B114" s="2" t="s">
         <x:v>726</x:v>
       </x:c>
-      <x:c r="B114" s="2" t="s">
+      <x:c r="C114" s="2" t="s">
+        <x:v>727</x:v>
+      </x:c>
+      <x:c r="D114" s="2" t="s">
         <x:v>728</x:v>
-      </x:c>
-      <x:c r="C114" s="2" t="s">
-        <x:v>729</x:v>
-      </x:c>
-      <x:c r="D114" s="2" t="s">
-        <x:v>730</x:v>
       </x:c>
       <x:c r="E114" s="2" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F114" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G114" s="2" t="s">
         <x:v>65</x:v>
@@ -13027,10 +13044,10 @@
     </x:row>
     <x:row r="115" ht="16.5">
       <x:c r="A115" s="2" t="s">
-        <x:v>726</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="B115" s="2" t="s">
-        <x:v>735</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="C115" s="2"/>
       <x:c r="D115" s="2"/>
@@ -13048,10 +13065,10 @@
     </x:row>
     <x:row r="116" ht="16.5">
       <x:c r="A116" s="3" t="s">
+        <x:v>737</x:v>
+      </x:c>
+      <x:c r="B116" s="3" t="s">
         <x:v>739</x:v>
-      </x:c>
-      <x:c r="B116" s="3" t="s">
-        <x:v>741</x:v>
       </x:c>
       <x:c r="C116" s="3"/>
       <x:c r="D116" s="3"/>
@@ -13070,7 +13087,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R606f5c685f4744a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05ba0b38dd1c4ef4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13085,10 +13102,10 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>757</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>758</x:v>
+        <x:v>756</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="16.5">
@@ -13096,7 +13113,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>759</x:v>
+        <x:v>757</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="16.5">
@@ -13104,7 +13121,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>760</x:v>
+        <x:v>758</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="16.5">
@@ -13112,7 +13129,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>761</x:v>
+        <x:v>759</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="16.5">
@@ -13120,13 +13137,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>762</x:v>
+        <x:v>760</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1911f1256b474a75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fddebc214844613"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13141,15 +13158,15 @@
   <x:sheetData>
     <x:row r="1" ht="27.950000762939453" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>763</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>762</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="16.5">
       <x:c r="A2" s="2" t="s">
-        <x:v>765</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>36</x:v>
@@ -13157,48 +13174,48 @@
     </x:row>
     <x:row r="3" ht="16.5">
       <x:c r="A3" s="2" t="s">
-        <x:v>766</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>767</x:v>
+        <x:v>765</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="16.5">
       <x:c r="A4" s="2" t="s">
-        <x:v>768</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>769</x:v>
+        <x:v>767</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="16.5">
       <x:c r="A5" s="2" t="s">
-        <x:v>770</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>771</x:v>
+        <x:v>769</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="16.5">
       <x:c r="A6" s="2" t="s">
-        <x:v>772</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="16.5">
       <x:c r="A7" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>773</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R730f1bbf038a4738"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28f0d5dbe81543f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
+++ b/医生画像仓库/99_资料来源/珠三角三甲医院官网入口台账.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="R2ab4198e6161431f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="R7f0d2d9028f94b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="Rdccb00b49d3a4bce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="R4f2881f123a44714"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="R334e36c6f8f54623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入口台账" sheetId="1" r:id="R35a96fc4e68849fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="Re4ac96476d09442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核清单" sheetId="3" r:id="R725db6e170d049a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="4" r:id="Rf91c64cea8d74035"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="5" r:id="Raeef376cf40c490d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3869,11 +3869,11 @@
       <x:c r="S16" s="2" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="T16" s="2" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="U16" s="2" t="s">
-        <x:v>65</x:v>
+      <x:c r="T16" s="2" t="str">
+        <x:v>入口锚文本：专家介绍；管理员裁决跳过（军队医院，2026-08-17）</x:v>
+      </x:c>
+      <x:c r="U16" s="2" t="str">
+        <x:v>跳过</x:v>
       </x:c>
       <x:c r="V16" s="2" t="s">
         <x:v>66</x:v>
@@ -10089,55 +10089,55 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R33ffe6539f694917"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="R36c21bb35cea42c3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="Rc66d91c0c35d4d9a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R030f50c53ea541b1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="R21d4bf280c194bb6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R40a7c891a40b45d1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="R1dec603ce7bc4442"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="R58eab9b80d2e48aa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="Re1b3f238751249e7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="Ra970982095f946f7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="Rf3517abf58164de7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="Rd24b1909ccb74f07"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R601ec40c61494945"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="R22b1120e94af448b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="R711f65b57d3c481c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="R664067dfb2fc4734"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="Rc6a5c2a1787d4d0d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="Ra997f5e3528a4f61"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="Rea5e0ab37ef94eca"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="Ra92777122ace4fa8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="Rdaf850a540994fa3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="Rc85eed91b6144c20"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Ra23d89b8997946dc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="Rc1060bd494074cbf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rf7ab0c0783b94e6a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="R48107b64042b4726"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="Rc37d29bef5314698"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="Rf69c924e779d4d52"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R2540eba63ed74ea6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R34b7bc34ef9845ea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="Rca14e5f1547c4f03"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="R5933b7a1c7754cb0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R9dfc103acc5b42b2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="Ree6b52da1e0e4ead"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="R5ab94717331449b9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R6dea6cb3368049eb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="R0e453b2d8a6446d2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R125cbeaceead4c41"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Rea06ff48f8474e22"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="Rd185949d182e491b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="Rbad2cdb4f39f4942"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R4fc587f1b8c44278"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="R23dc279fa1dd46d8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="R8f2a81d061df49ae"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R36ff7854aadb465e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="R613fe9d9b6cb4cda"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="Rbd7e3f60bf554d1a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="R4fed7d6460dd40f7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="R136946bb5764437d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="R78d3d3f8b62d4b86"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="R4be128aee86144a3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="Ra305d03147914d05"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="R6281ab4f3f5e49f5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="R726407611f4348d9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="Rc9cc13c2db4a4792"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="Ra3e6bd4daa4240ad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="R4b4842ab5fba413d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="R4a64e278c3d74284"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="Rcffe16ceb53e4a54"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="Ra465be85ba5d455b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="R83633dd487a84111"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="Rd3fa6611a7ca407a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="R338456d823954414"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="Ra82d65eaf79e4d1a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="R90d0c80c81194da1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="R668c5ff40575428f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="Re0c5d096b2f14a1f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="Rfb9e2443a6a04694"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="Rbfdbe7c2ffaf4566"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="Rc6316dbd6c0142f4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="R157868301bc346de"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="R2232a73acf1e4d4f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="R11b26225e2e8460d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="R93309c90caf74e09"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R646c8032f9014c55"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="R8a67db325f5f445f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="Rad71da3aa6794bfb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="R87b95a42b1c14b98"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="R01536b0440d14f93"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="Rdeaeb229aa7d4ee8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="R66cd7749dcc54689"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="Red24c9777efe4dee"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="R60ec3ac2c8f24fd1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="Rfd584c02cd2446cb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="R613b93de76f84ebf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="R4dbc6c23c59e47e0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="R8111685614984d76"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="Rfbc3be5f60c84a5f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="Rac1a26b07dac4ef9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="R16fdfd2a36b547f3"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R149744666abf47a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d8e5008a1fc410e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10416,7 +10416,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra227091762b6444d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d48e9a0bb444015"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13087,7 +13087,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05ba0b38dd1c4ef4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb26dfecb62214332"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13143,7 +13143,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fddebc214844613"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re58d9c4f0b2842b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13215,7 +13215,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28f0d5dbe81543f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R435137deb8204811"/>
   </x:tableParts>
 </x:worksheet>
 </file>